--- a/dati.xlsx
+++ b/dati.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C41EFA4-E3D0-4528-9A1F-259D3682162B}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E36D54C5-5DAF-4063-BA06-3036A4427FFC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -988,7 +988,7 @@
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46253</v>
+            <v>46264</v>
           </cell>
         </row>
       </sheetData>
@@ -1050,19 +1050,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.76738889522792042</v>
+            <v>0.79688980789771113</v>
           </cell>
           <cell r="G4">
-            <v>0.59677419354838712</v>
+            <v>0.64516129032258063</v>
           </cell>
           <cell r="H4">
-            <v>-2.4164115526934572E-3</v>
+            <v>1.362570165323184E-3</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>219.4619967329682</v>
+            <v>221.06500269348177</v>
           </cell>
         </row>
         <row r="5">
@@ -1073,7 +1073,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.82915231930391031</v>
+            <v>0.75379315377491096</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1085,7 +1085,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>302.40592018984574</v>
+            <v>296.64554483642451</v>
           </cell>
         </row>
         <row r="6">
@@ -1096,19 +1096,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.91681894689734511</v>
+            <v>0.87697950993898988</v>
           </cell>
           <cell r="G6">
-            <v>0.97329993279159288</v>
+            <v>0.97098172923692694</v>
           </cell>
           <cell r="H6">
-            <v>1.3299932791592917E-2</v>
+            <v>1.0981729236926974E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>224.84846202134338</v>
+            <v>223.49683206106872</v>
           </cell>
         </row>
         <row r="7">
@@ -1119,19 +1119,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.62458776074800981</v>
+            <v>0.60949386082725154</v>
           </cell>
           <cell r="G7">
-            <v>0.5892857142857143</v>
+            <v>0.625</v>
           </cell>
           <cell r="H7">
-            <v>-3.2404955073082865E-2</v>
+            <v>-2.3780413411657614E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>197.04982456140351</v>
+            <v>198.29874256868737</v>
           </cell>
         </row>
         <row r="8">
@@ -1142,19 +1142,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.50473576740689596</v>
+            <v>0.49784268050635339</v>
           </cell>
           <cell r="G8">
-            <v>0.47058823529411764</v>
+            <v>0.5</v>
           </cell>
           <cell r="H8">
-            <v>-3.5093084706142662E-2</v>
+            <v>-1.4493853854232396E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>264.88638497652585</v>
+            <v>261.18732932823593</v>
           </cell>
         </row>
         <row r="9">
@@ -1165,19 +1165,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.46046782385559709</v>
+            <v>0.51322949005364515</v>
           </cell>
           <cell r="G9">
             <v>0.75</v>
           </cell>
           <cell r="H9">
-            <v>1.5298582461048026E-2</v>
+            <v>1.4147998146011699E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>137.93966623876764</v>
+            <v>137.2729340409401</v>
           </cell>
         </row>
         <row r="10">
@@ -1188,19 +1188,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.73588770338853715</v>
+            <v>0.76921669265352666</v>
           </cell>
           <cell r="G10">
-            <v>0.47368421052631576</v>
+            <v>0.44736842105263158</v>
           </cell>
           <cell r="H10">
-            <v>4.0119552990118909E-4</v>
+            <v>-7.2713550278350348E-4</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>191.9507587988376</v>
+            <v>192.30308157099697</v>
           </cell>
         </row>
       </sheetData>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D2" s="48">
         <f>'[1]Riepilogo mese per Commessa'!$D$1-1</f>
-        <v>46252</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1923,19 +1923,19 @@
       </c>
       <c r="D4" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.76738889522792042</v>
+        <v>0.79688980789771113</v>
       </c>
       <c r="E4" s="34">
         <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>0.11745982010277789</v>
+        <v>0.1469607327725686</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.59677419354838712</v>
+        <v>0.64516129032258063</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>-2.4164115526934572E-3</v>
+        <v>1.362570165323184E-3</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1943,11 +1943,11 @@
       </c>
       <c r="I4" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>219.4619967329682</v>
+        <v>221.06500269348177</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-5.4337269427940656E-2</v>
+        <v>-4.7429909537348595E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1960,11 +1960,11 @@
       </c>
       <c r="D5" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.82915231930391031</v>
+        <v>0.75379315377491096</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" si="0"/>
-        <v>6.8274831495185095E-2</v>
+        <v>-7.0843340338142546E-3</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1980,11 +1980,11 @@
       </c>
       <c r="I5" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>302.40592018984574</v>
+        <v>296.64554483642451</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" si="1"/>
-        <v>0.20543796697585998</v>
+        <v>0.18247619707834356</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -1997,19 +1997,19 @@
       </c>
       <c r="D6" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.91681894689734511</v>
+        <v>0.87697950993898988</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" si="0"/>
-        <v>0.12803140017159431</v>
+        <v>8.8191963213239077E-2</v>
       </c>
       <c r="F6" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.97329993279159288</v>
+        <v>0.97098172923692694</v>
       </c>
       <c r="G6" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.3299932791592917E-2</v>
+        <v>1.0981729236926974E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -2017,11 +2017,11 @@
       </c>
       <c r="I6" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>224.84846202134338</v>
+        <v>223.49683206106872</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" si="1"/>
-        <v>2.8111840464365479E-2</v>
+        <v>2.1931559071322847E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -2034,19 +2034,19 @@
       </c>
       <c r="D7" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.62458776074800981</v>
+        <v>0.60949386082725154</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
-        <v>7.1138386367406437E-3</v>
+        <v>-7.9800612840176255E-3</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.5892857142857143</v>
+        <v>0.625</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>-3.2404955073082865E-2</v>
+        <v>-2.3780413411657614E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2054,11 +2054,11 @@
       </c>
       <c r="I7" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>197.04982456140351</v>
+        <v>198.29874256868737</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" si="1"/>
-        <v>-1.8470346305063116E-2</v>
+        <v>-1.224933057002648E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="D8" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.50473576740689596</v>
+        <v>0.49784268050635339</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" si="0"/>
-        <v>-0.12796423259310408</v>
+        <v>-0.13485731949364665</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.47058823529411764</v>
+        <v>0.5</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-3.5093084706142662E-2</v>
+        <v>-1.4493853854232396E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2091,11 +2091,11 @@
       </c>
       <c r="I8" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>264.88638497652585</v>
+        <v>261.18732932823593</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="1"/>
-        <v>0.807723120686207</v>
+        <v>0.7824788318160516</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2108,11 +2108,11 @@
       </c>
       <c r="D9" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.46046782385559709</v>
+        <v>0.51322949005364515</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" si="0"/>
-        <v>-0.21523771466942282</v>
+        <v>-0.16247604847137476</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.5298582461048026E-2</v>
+        <v>1.4147998146011699E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2128,11 +2128,11 @@
       </c>
       <c r="I9" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>137.93966623876764</v>
+        <v>137.2729340409401</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" si="1"/>
-        <v>-7.9251522801592519E-2</v>
+        <v>-8.3701966046730109E-2</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2145,19 +2145,19 @@
       </c>
       <c r="D10" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.73588770338853715</v>
+        <v>0.76921669265352666</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" si="0"/>
-        <v>8.5704050393080156E-2</v>
+        <v>0.11903303965806966</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.47368421052631576</v>
+        <v>0.44736842105263158</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.0119552990118909E-4</v>
+        <v>-7.2713550278350348E-4</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2165,11 +2165,11 @@
       </c>
       <c r="I10" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>191.9507587988376</v>
+        <v>192.30308157099697</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="1"/>
-        <v>3.7992393540718129E-2</v>
+        <v>3.989761319111744E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2241,11 +2241,11 @@
       </c>
       <c r="F5" s="41">
         <f>IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G5" s="42">
         <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
-        <v>4.8</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C6" s="43">
         <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="D6" s="43">
         <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G6" s="42">
         <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="E7" s="41">
         <f>IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="41">
         <f>IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G7" s="42">
         <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="C8" s="43">
         <f>IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="D8" s="43">
         <f>IF('Dati Comparti'!F7="","",IF('Dati Comparti'!F7&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F7&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F7&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F7&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F7&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="G8" s="42">
         <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>1.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -2439,7 +2439,7 @@
       <c r="F15" s="56"/>
       <c r="G15" s="1">
         <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -2448,14 +2448,14 @@
       </c>
       <c r="C16" s="60" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
-        <v>Editoria</v>
+        <v>Centro Servizi</v>
       </c>
       <c r="D16" s="56"/>
       <c r="E16" s="56"/>
       <c r="F16" s="56"/>
       <c r="G16" s="2">
         <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>7</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2464,14 +2464,14 @@
       </c>
       <c r="C17" s="58" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
+        <v>Medicale</v>
       </c>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
       <c r="F17" s="56"/>
       <c r="G17" s="3">
         <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>4.8</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -2480,14 +2480,14 @@
       </c>
       <c r="C18" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Medicale</v>
+        <v>Editoria</v>
       </c>
       <c r="D18" s="56"/>
       <c r="E18" s="56"/>
       <c r="F18" s="56"/>
       <c r="G18" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>4.4000000000000004</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -2503,7 +2503,7 @@
       <c r="F19" s="56"/>
       <c r="G19" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>1.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -2941,10 +2941,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="52">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G16" s="52">
-        <v>4.8</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2955,7 +2955,7 @@
         <v>66</v>
       </c>
       <c r="C17" s="52">
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="D17" s="52">
         <v>10</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="52">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2984,13 +2984,13 @@
         <v>10</v>
       </c>
       <c r="E18" s="52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="52">
         <v>4</v>
       </c>
       <c r="G18" s="52">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3001,7 +3001,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="52">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="D19" s="52">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>6</v>
       </c>
       <c r="G19" s="52">
-        <v>1.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E36D54C5-5DAF-4063-BA06-3036A4427FFC}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55251A42-8746-4DC2-8F44-949912EAB2BD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -988,7 +988,7 @@
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46264</v>
+            <v>46265</v>
           </cell>
         </row>
       </sheetData>
@@ -1050,19 +1050,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.79688980789771113</v>
+            <v>0.77653810639820109</v>
           </cell>
           <cell r="G4">
             <v>0.64516129032258063</v>
           </cell>
           <cell r="H4">
-            <v>1.362570165323184E-3</v>
+            <v>2.433534075434582E-3</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>221.06500269348177</v>
+            <v>221.75168545691463</v>
           </cell>
         </row>
         <row r="5">
@@ -1073,7 +1073,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.75379315377491096</v>
+            <v>0.73773928058182925</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1085,7 +1085,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>296.64554483642451</v>
+            <v>296.03308561539245</v>
           </cell>
         </row>
         <row r="6">
@@ -1096,19 +1096,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.87697950993898988</v>
+            <v>0.82377911259006886</v>
           </cell>
           <cell r="G6">
-            <v>0.97098172923692694</v>
+            <v>0.9715587079726018</v>
           </cell>
           <cell r="H6">
-            <v>1.0981729236926974E-2</v>
+            <v>1.1558707972601834E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>223.49683206106872</v>
+            <v>223.08971835522314</v>
           </cell>
         </row>
         <row r="7">
@@ -1119,19 +1119,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.60949386082725154</v>
+            <v>0.63385019465201109</v>
           </cell>
           <cell r="G7">
-            <v>0.625</v>
+            <v>0.6071428571428571</v>
           </cell>
           <cell r="H7">
-            <v>-2.3780413411657614E-2</v>
+            <v>-2.8311081710491879E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>198.29874256868737</v>
+            <v>197.94091469862531</v>
           </cell>
         </row>
         <row r="8">
@@ -1142,19 +1142,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.49784268050635339</v>
+            <v>0.48732535537830229</v>
           </cell>
           <cell r="G8">
             <v>0.5</v>
           </cell>
           <cell r="H8">
-            <v>-1.4493853854232396E-2</v>
+            <v>-1.4655916862017738E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>261.18732932823593</v>
+            <v>260.82296650717706</v>
           </cell>
         </row>
         <row r="9">
@@ -1165,19 +1165,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.51322949005364515</v>
+            <v>0.60320515955610055</v>
           </cell>
           <cell r="G9">
             <v>0.75</v>
           </cell>
           <cell r="H9">
-            <v>1.4147998146011699E-2</v>
+            <v>1.440078969061093E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>137.2729340409401</v>
+            <v>136.98113905325442</v>
           </cell>
         </row>
         <row r="10">
@@ -1188,19 +1188,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.76921669265352666</v>
+            <v>0.75699017684063397</v>
           </cell>
           <cell r="G10">
-            <v>0.44736842105263158</v>
+            <v>0.47368421052631576</v>
           </cell>
           <cell r="H10">
-            <v>-7.2713550278350348E-4</v>
+            <v>1.1930826810205707E-3</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>192.30308157099697</v>
+            <v>192.55856689888213</v>
           </cell>
         </row>
       </sheetData>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D2" s="48">
         <f>'[1]Riepilogo mese per Commessa'!$D$1-1</f>
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1923,11 +1923,11 @@
       </c>
       <c r="D4" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.79688980789771113</v>
+        <v>0.77653810639820109</v>
       </c>
       <c r="E4" s="34">
         <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>0.1469607327725686</v>
+        <v>0.12660903127305856</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.362570165323184E-3</v>
+        <v>2.433534075434582E-3</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1943,11 +1943,11 @@
       </c>
       <c r="I4" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>221.06500269348177</v>
+        <v>221.75168545691463</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-4.7429909537348595E-2</v>
+        <v>-4.4470990422551662E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1960,11 +1960,11 @@
       </c>
       <c r="D5" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.75379315377491096</v>
+        <v>0.73773928058182925</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" si="0"/>
-        <v>-7.0843340338142546E-3</v>
+        <v>-2.3138207226895968E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1980,11 +1980,11 @@
       </c>
       <c r="I5" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>296.64554483642451</v>
+        <v>296.03308561539245</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" si="1"/>
-        <v>0.18247619707834356</v>
+        <v>0.18003483747204677</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -1997,19 +1997,19 @@
       </c>
       <c r="D6" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.87697950993898988</v>
+        <v>0.82377911259006886</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" si="0"/>
-        <v>8.8191963213239077E-2</v>
+        <v>3.4991565864318064E-2</v>
       </c>
       <c r="F6" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.97098172923692694</v>
+        <v>0.9715587079726018</v>
       </c>
       <c r="G6" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.0981729236926974E-2</v>
+        <v>1.1558707972601834E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -2017,11 +2017,11 @@
       </c>
       <c r="I6" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>223.49683206106872</v>
+        <v>223.08971835522314</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" si="1"/>
-        <v>2.1931559071322847E-2</v>
+        <v>2.007004568745353E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -2034,19 +2034,19 @@
       </c>
       <c r="D7" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.60949386082725154</v>
+        <v>0.63385019465201109</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
-        <v>-7.9800612840176255E-3</v>
+        <v>1.6376272540741921E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.625</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>-2.3780413411657614E-2</v>
+        <v>-2.8311081710491879E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2054,11 +2054,11 @@
       </c>
       <c r="I7" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>198.29874256868737</v>
+        <v>197.94091469862531</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" si="1"/>
-        <v>-1.224933057002648E-2</v>
+        <v>-1.4031715640229743E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2071,11 +2071,11 @@
       </c>
       <c r="D8" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.49784268050635339</v>
+        <v>0.48732535537830229</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" si="0"/>
-        <v>-0.13485731949364665</v>
+        <v>-0.14537464462169775</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-1.4493853854232396E-2</v>
+        <v>-1.4655916862017738E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2091,11 +2091,11 @@
       </c>
       <c r="I8" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>261.18732932823593</v>
+        <v>260.82296650717706</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="1"/>
-        <v>0.7824788318160516</v>
+        <v>0.77999222950916092</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2108,11 +2108,11 @@
       </c>
       <c r="D9" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.51322949005364515</v>
+        <v>0.60320515955610055</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" si="0"/>
-        <v>-0.16247604847137476</v>
+        <v>-7.2500378968919366E-2</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.4147998146011699E-2</v>
+        <v>1.440078969061093E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2128,11 +2128,11 @@
       </c>
       <c r="I9" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>137.2729340409401</v>
+        <v>136.98113905325442</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" si="1"/>
-        <v>-8.3701966046730109E-2</v>
+        <v>-8.5649700138682019E-2</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2145,19 +2145,19 @@
       </c>
       <c r="D10" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.76921669265352666</v>
+        <v>0.75699017684063397</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" si="0"/>
-        <v>0.11903303965806966</v>
+        <v>0.10680652384517697</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.44736842105263158</v>
+        <v>0.47368421052631576</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>-7.2713550278350348E-4</v>
+        <v>1.1930826810205707E-3</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2165,11 +2165,11 @@
       </c>
       <c r="I10" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>192.30308157099697</v>
+        <v>192.55856689888213</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="1"/>
-        <v>3.989761319111744E-2</v>
+        <v>4.1279174945108625E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C6" s="43">
         <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="D6" s="43">
         <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G6" s="42">
         <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C7" s="41">
         <f>IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D7" s="41">
         <f>IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="E7" s="41">
         <f>IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="41">
         <f>IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G7" s="42">
         <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="C8" s="43">
         <f>IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="D8" s="43">
         <f>IF('Dati Comparti'!F7="","",IF('Dati Comparti'!F7&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F7&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F7&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F7&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F7&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="G8" s="42">
         <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>-0.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -2439,7 +2439,7 @@
       <c r="F15" s="56"/>
       <c r="G15" s="1">
         <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -2487,7 +2487,7 @@
       <c r="F18" s="56"/>
       <c r="G18" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -2503,7 +2503,7 @@
       <c r="F19" s="56"/>
       <c r="G19" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>-0.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -2955,7 +2955,7 @@
         <v>66</v>
       </c>
       <c r="C17" s="52">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="D17" s="52">
         <v>10</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="52">
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2978,19 +2978,19 @@
         <v>67</v>
       </c>
       <c r="C18" s="52">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D18" s="52">
         <v>10</v>
       </c>
       <c r="E18" s="52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="52">
         <v>4</v>
       </c>
       <c r="G18" s="52">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3001,7 +3001,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="52">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="D19" s="52">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>6</v>
       </c>
       <c r="G19" s="52">
-        <v>-0.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55251A42-8746-4DC2-8F44-949912EAB2BD}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41067F55-E91B-431D-B4FD-80481E747C95}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="810" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -937,6 +937,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="db iniziale"/>
       <sheetName val="Code_Commesse"/>
@@ -1007,7 +1010,6 @@
           <cell r="D2" t="str">
             <v>PRODUTTIVITÀ</v>
           </cell>
-          <cell r="E2"/>
           <cell r="G2" t="str">
             <v>IUQ</v>
           </cell>
@@ -1017,7 +1019,6 @@
           <cell r="I2" t="str">
             <v>TMG</v>
           </cell>
-          <cell r="J2"/>
         </row>
         <row r="3">
           <cell r="B3" t="str">
@@ -1880,8 +1881,8 @@
         <v>56</v>
       </c>
       <c r="D2" s="48">
-        <f>'[1]Riepilogo mese per Commessa'!$D$1-1</f>
-        <v>46264</v>
+        <f ca="1">'[1]Riepilogo mese per Commessa'!$D$1</f>
+        <v>46265</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1922,11 +1923,11 @@
         <v>0.64992907512514253</v>
       </c>
       <c r="D4" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
         <v>0.77653810639820109</v>
       </c>
       <c r="E4" s="34">
-        <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
+        <f t="shared" ref="E4:E10" ca="1" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
         <v>0.12660903127305856</v>
       </c>
       <c r="F4" s="35">
@@ -1942,11 +1943,11 @@
         <v>232.07216445995408</v>
       </c>
       <c r="I4" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
         <v>221.75168545691463</v>
       </c>
       <c r="J4" s="34">
-        <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
+        <f t="shared" ref="J4:J10" ca="1" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
         <v>-4.4470990422551662E-2</v>
       </c>
     </row>
@@ -1959,11 +1960,11 @@
         <v>0.76087748780872522</v>
       </c>
       <c r="D5" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
         <v>0.73773928058182925</v>
       </c>
       <c r="E5" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-2.3138207226895968E-2</v>
       </c>
       <c r="F5" s="35">
@@ -1979,11 +1980,11 @@
         <v>250.86808983502152</v>
       </c>
       <c r="I5" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
         <v>296.03308561539245</v>
       </c>
       <c r="J5" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0.18003483747204677</v>
       </c>
     </row>
@@ -1996,19 +1997,19 @@
         <v>0.7887875467257508</v>
       </c>
       <c r="D6" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>0.82377911259006886</v>
       </c>
       <c r="E6" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>3.4991565864318064E-2</v>
       </c>
       <c r="F6" s="35">
-        <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>0.9715587079726018</v>
       </c>
       <c r="G6" s="36">
-        <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>1.1558707972601834E-2</v>
       </c>
       <c r="H6" s="37">
@@ -2016,11 +2017,11 @@
         <v>218.70039150583702</v>
       </c>
       <c r="I6" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>223.08971835522314</v>
       </c>
       <c r="J6" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>2.007004568745353E-2</v>
       </c>
     </row>
@@ -2033,11 +2034,11 @@
         <v>0.61747392211126917</v>
       </c>
       <c r="D7" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
         <v>0.63385019465201109</v>
       </c>
       <c r="E7" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>1.6376272540741921E-2</v>
       </c>
       <c r="F7" s="35">
@@ -2053,11 +2054,11 @@
         <v>200.75789235670646</v>
       </c>
       <c r="I7" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
         <v>197.94091469862531</v>
       </c>
       <c r="J7" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-1.4031715640229743E-2</v>
       </c>
     </row>
@@ -2070,11 +2071,11 @@
         <v>0.63270000000000004</v>
       </c>
       <c r="D8" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
         <v>0.48732535537830229</v>
       </c>
       <c r="E8" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-0.14537464462169775</v>
       </c>
       <c r="F8" s="35">
@@ -2090,11 +2091,11 @@
         <v>146.53039613498757</v>
       </c>
       <c r="I8" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
         <v>260.82296650717706</v>
       </c>
       <c r="J8" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0.77999222950916092</v>
       </c>
     </row>
@@ -2107,11 +2108,11 @@
         <v>0.67570553852501991</v>
       </c>
       <c r="D9" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
         <v>0.60320515955610055</v>
       </c>
       <c r="E9" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-7.2500378968919366E-2</v>
       </c>
       <c r="F9" s="35">
@@ -2127,11 +2128,11 @@
         <v>149.81253801090318</v>
       </c>
       <c r="I9" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
         <v>136.98113905325442</v>
       </c>
       <c r="J9" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-8.5649700138682019E-2</v>
       </c>
     </row>
@@ -2144,11 +2145,11 @@
         <v>0.650183652995457</v>
       </c>
       <c r="D10" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
         <v>0.75699017684063397</v>
       </c>
       <c r="E10" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0.10680652384517697</v>
       </c>
       <c r="F10" s="35">
@@ -2164,11 +2165,11 @@
         <v>184.92501485879896</v>
       </c>
       <c r="I10" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
         <v>192.55856689888213</v>
       </c>
       <c r="J10" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>4.1279174945108625E-2</v>
       </c>
     </row>
@@ -2228,7 +2229,7 @@
         <v>Centro Servizi</v>
       </c>
       <c r="C5" s="41">
-        <f>IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>10</v>
       </c>
       <c r="D5" s="41">
@@ -2240,11 +2241,11 @@
         <v>0</v>
       </c>
       <c r="F5" s="41">
-        <f>IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>6</v>
       </c>
       <c r="G5" s="42">
-        <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -2254,7 +2255,7 @@
         <v>Editoria</v>
       </c>
       <c r="C6" s="43">
-        <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-5</v>
       </c>
       <c r="D6" s="43">
@@ -2266,11 +2267,11 @@
         <v>4</v>
       </c>
       <c r="F6" s="43">
-        <f>IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>0</v>
       </c>
       <c r="G6" s="42">
-        <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
         <v>1.8</v>
       </c>
     </row>
@@ -2280,23 +2281,23 @@
         <v>Gori</v>
       </c>
       <c r="C7" s="41">
-        <f>IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>4</v>
       </c>
       <c r="D7" s="41">
-        <f>IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
+        <f ca="1">IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
         <v>10</v>
       </c>
       <c r="E7" s="41">
-        <f>IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
+        <f ca="1">IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>2</v>
       </c>
       <c r="F7" s="41">
-        <f>IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G7" s="42">
-        <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
         <v>5.4</v>
       </c>
     </row>
@@ -2306,7 +2307,7 @@
         <v>Idrico</v>
       </c>
       <c r="C8" s="43">
-        <f>IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>2</v>
       </c>
       <c r="D8" s="43">
@@ -2318,11 +2319,11 @@
         <v>0</v>
       </c>
       <c r="F8" s="43">
-        <f>IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>6</v>
       </c>
       <c r="G8" s="42">
-        <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
         <v>1.4</v>
       </c>
     </row>
@@ -2332,7 +2333,7 @@
         <v>Igiene Ambientale</v>
       </c>
       <c r="C9" s="41">
-        <f>IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D9" s="41">
@@ -2344,11 +2345,11 @@
         <v>0</v>
       </c>
       <c r="F9" s="41">
-        <f>IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>0</v>
       </c>
       <c r="G9" s="42">
-        <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
         <v>-4</v>
       </c>
     </row>
@@ -2357,7 +2358,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="43">
-        <f>IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D10" s="43">
@@ -2369,11 +2370,11 @@
         <v>2</v>
       </c>
       <c r="F10" s="43">
-        <f>IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>8</v>
       </c>
       <c r="G10" s="42">
-        <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
         <v>-2.2000000000000002</v>
       </c>
     </row>
@@ -2382,7 +2383,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="41">
-        <f>IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>10</v>
       </c>
       <c r="D11" s="41">
@@ -2394,11 +2395,11 @@
         <v>0</v>
       </c>
       <c r="F11" s="41">
-        <f>IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G11" s="42">
-        <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
         <v>4.4000000000000004</v>
       </c>
     </row>
@@ -2431,14 +2432,14 @@
         <v>13</v>
       </c>
       <c r="C15" s="61" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
         <v>Gori</v>
       </c>
       <c r="D15" s="56"/>
       <c r="E15" s="56"/>
       <c r="F15" s="56"/>
       <c r="G15" s="1">
-        <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
         <v>5.4</v>
       </c>
     </row>
@@ -2447,14 +2448,14 @@
         <v>14</v>
       </c>
       <c r="C16" s="60" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
         <v>Centro Servizi</v>
       </c>
       <c r="D16" s="56"/>
       <c r="E16" s="56"/>
       <c r="F16" s="56"/>
       <c r="G16" s="2">
-        <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -2463,14 +2464,14 @@
         <v>15</v>
       </c>
       <c r="C17" s="58" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
         <v>Medicale</v>
       </c>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
       <c r="F17" s="56"/>
       <c r="G17" s="3">
-        <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
         <v>4.4000000000000004</v>
       </c>
     </row>
@@ -2479,14 +2480,14 @@
         <v>16</v>
       </c>
       <c r="C18" s="57" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
         <v>Editoria</v>
       </c>
       <c r="D18" s="56"/>
       <c r="E18" s="56"/>
       <c r="F18" s="56"/>
       <c r="G18" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
         <v>1.8</v>
       </c>
     </row>
@@ -2495,14 +2496,14 @@
         <v>17</v>
       </c>
       <c r="C19" s="57" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
         <v>Idrico</v>
       </c>
       <c r="D19" s="56"/>
       <c r="E19" s="56"/>
       <c r="F19" s="56"/>
       <c r="G19" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
         <v>1.4</v>
       </c>
     </row>
@@ -2511,14 +2512,14 @@
         <v>18</v>
       </c>
       <c r="C20" s="57" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
       <c r="D20" s="56"/>
       <c r="E20" s="56"/>
       <c r="F20" s="56"/>
       <c r="G20" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
         <v>-2.2000000000000002</v>
       </c>
     </row>
@@ -2527,14 +2528,14 @@
         <v>19</v>
       </c>
       <c r="C21" s="57" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>Igiene Ambientale</v>
       </c>
       <c r="D21" s="56"/>
       <c r="E21" s="56"/>
       <c r="F21" s="56"/>
       <c r="G21" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
         <v>-4</v>
       </c>
     </row>

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41067F55-E91B-431D-B4FD-80481E747C95}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7BEB3DE-47EA-444F-B85B-EC3DE80E0B09}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="810" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="75">
   <si>
     <t>🏆  SCORING COMPARTI</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
   </si>
 </sst>
 </file>
@@ -970,7 +973,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="B1">
-            <v>46235</v>
+            <v>46266</v>
           </cell>
         </row>
       </sheetData>
@@ -991,7 +994,7 @@
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46265</v>
+            <v>46278</v>
           </cell>
         </row>
       </sheetData>
@@ -1010,6 +1013,7 @@
           <cell r="D2" t="str">
             <v>PRODUTTIVITÀ</v>
           </cell>
+          <cell r="E2"/>
           <cell r="G2" t="str">
             <v>IUQ</v>
           </cell>
@@ -1019,6 +1023,7 @@
           <cell r="I2" t="str">
             <v>TMG</v>
           </cell>
+          <cell r="J2"/>
         </row>
         <row r="3">
           <cell r="B3" t="str">
@@ -1051,19 +1056,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.77653810639820109</v>
+            <v>0.75444606828820626</v>
           </cell>
           <cell r="G4">
             <v>0.64516129032258063</v>
           </cell>
           <cell r="H4">
-            <v>2.433534075434582E-3</v>
+            <v>-9.5379938521738129E-4</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>221.75168545691463</v>
+            <v>221.41514400743264</v>
           </cell>
         </row>
         <row r="5">
@@ -1074,7 +1079,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.73773928058182925</v>
+            <v>0.76350735068440279</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1086,7 +1091,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>296.03308561539245</v>
+            <v>282.34175652851758</v>
           </cell>
         </row>
         <row r="6">
@@ -1097,19 +1102,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.82377911259006886</v>
+            <v>0.76814494125833666</v>
           </cell>
           <cell r="G6">
-            <v>0.9715587079726018</v>
+            <v>0.96789812296876032</v>
           </cell>
           <cell r="H6">
-            <v>1.1558707972601834E-2</v>
+            <v>7.8981229687603571E-3</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>223.08971835522314</v>
+            <v>219.03131638456793</v>
           </cell>
         </row>
         <row r="7">
@@ -1120,19 +1125,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.63385019465201109</v>
+            <v>0.61652751879606094</v>
           </cell>
           <cell r="G7">
-            <v>0.6071428571428571</v>
+            <v>0.75</v>
           </cell>
           <cell r="H7">
-            <v>-2.8311081710491879E-2</v>
+            <v>1.8847809915817124E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>197.94091469862531</v>
+            <v>193.15833773435438</v>
           </cell>
         </row>
         <row r="8">
@@ -1143,19 +1148,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.48732535537830229</v>
+            <v>0.40635494702968061</v>
           </cell>
           <cell r="G8">
-            <v>0.5</v>
+            <v>0.5625</v>
           </cell>
           <cell r="H8">
-            <v>-1.4655916862017738E-2</v>
+            <v>1.4974432573128546E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>260.82296650717706</v>
+            <v>253.37864077669903</v>
           </cell>
         </row>
         <row r="9">
@@ -1166,19 +1171,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.60320515955610055</v>
+            <v>0.48211556152774671</v>
           </cell>
           <cell r="G9">
             <v>0.75</v>
           </cell>
           <cell r="H9">
-            <v>1.440078969061093E-2</v>
+            <v>3.040825089971505E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>136.98113905325442</v>
+            <v>141.34261603375526</v>
           </cell>
         </row>
         <row r="10">
@@ -1189,19 +1194,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.75699017684063397</v>
+            <v>0.75875011799917746</v>
           </cell>
           <cell r="G10">
-            <v>0.47368421052631576</v>
+            <v>0.52631578947368418</v>
           </cell>
           <cell r="H10">
-            <v>1.1930826810205707E-3</v>
+            <v>4.8107644875554868E-3</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>192.55856689888213</v>
+            <v>196.07845752743589</v>
           </cell>
         </row>
       </sheetData>
@@ -1873,7 +1878,7 @@
       </c>
       <c r="D1" s="49">
         <f>'[1]db iniziale'!$B$1</f>
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
@@ -1881,8 +1886,8 @@
         <v>56</v>
       </c>
       <c r="D2" s="48">
-        <f ca="1">'[1]Riepilogo mese per Commessa'!$D$1</f>
-        <v>46265</v>
+        <f>'[1]Riepilogo mese per Commessa'!$D$1</f>
+        <v>46278</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1923,12 +1928,12 @@
         <v>0.64992907512514253</v>
       </c>
       <c r="D4" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.77653810639820109</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.75444606828820626</v>
       </c>
       <c r="E4" s="34">
-        <f t="shared" ref="E4:E10" ca="1" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>0.12660903127305856</v>
+        <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
+        <v>0.10451699316306373</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1936,19 +1941,19 @@
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>2.433534075434582E-3</v>
+        <v>-9.5379938521738129E-4</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
         <v>232.07216445995408</v>
       </c>
       <c r="I4" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>221.75168545691463</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>221.41514400743264</v>
       </c>
       <c r="J4" s="34">
-        <f t="shared" ref="J4:J10" ca="1" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-4.4470990422551662E-2</v>
+        <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
+        <v>-4.5921149041381011E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1960,12 +1965,12 @@
         <v>0.76087748780872522</v>
       </c>
       <c r="D5" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.73773928058182925</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.76350735068440279</v>
       </c>
       <c r="E5" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>-2.3138207226895968E-2</v>
+        <f t="shared" si="0"/>
+        <v>2.6298628756775688E-3</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1980,12 +1985,12 @@
         <v>250.86808983502152</v>
       </c>
       <c r="I5" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>296.03308561539245</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>282.34175652851758</v>
       </c>
       <c r="J5" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.18003483747204677</v>
+        <f t="shared" si="1"/>
+        <v>0.12545902794649608</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -1997,32 +2002,32 @@
         <v>0.7887875467257508</v>
       </c>
       <c r="D6" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.82377911259006886</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.76814494125833666</v>
       </c>
       <c r="E6" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.4991565864318064E-2</v>
+        <f t="shared" si="0"/>
+        <v>-2.0642605467414143E-2</v>
       </c>
       <c r="F6" s="35">
-        <f ca="1">INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.9715587079726018</v>
+        <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.96789812296876032</v>
       </c>
       <c r="G6" s="36">
-        <f ca="1">INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.1558707972601834E-2</v>
+        <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>7.8981229687603571E-3</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>218.70039150583702</v>
       </c>
       <c r="I6" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>223.08971835522314</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>219.03131638456793</v>
       </c>
       <c r="J6" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.007004568745353E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.513142598659131E-3</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -2034,32 +2039,32 @@
         <v>0.61747392211126917</v>
       </c>
       <c r="D7" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.63385019465201109</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.61652751879606094</v>
       </c>
       <c r="E7" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>1.6376272540741921E-2</v>
+        <f t="shared" si="0"/>
+        <v>-9.4640331520823295E-4</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.6071428571428571</v>
+        <v>0.75</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>-2.8311081710491879E-2</v>
+        <v>1.8847809915817124E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
         <v>200.75789235670646</v>
       </c>
       <c r="I7" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>197.94091469862531</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>193.15833773435438</v>
       </c>
       <c r="J7" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.4031715640229743E-2</v>
+        <f t="shared" si="1"/>
+        <v>-3.7854325591589716E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2071,32 +2076,32 @@
         <v>0.63270000000000004</v>
       </c>
       <c r="D8" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.48732535537830229</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.40635494702968061</v>
       </c>
       <c r="E8" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.14537464462169775</v>
+        <f t="shared" si="0"/>
+        <v>-0.22634505297031943</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.5</v>
+        <v>0.5625</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-1.4655916862017738E-2</v>
+        <v>1.4974432573128546E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
         <v>146.53039613498757</v>
       </c>
       <c r="I8" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>260.82296650717706</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>253.37864077669903</v>
       </c>
       <c r="J8" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.77999222950916092</v>
+        <f t="shared" si="1"/>
+        <v>0.72918826032026907</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2108,12 +2113,12 @@
         <v>0.67570553852501991</v>
       </c>
       <c r="D9" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.60320515955610055</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.48211556152774671</v>
       </c>
       <c r="E9" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>-7.2500378968919366E-2</v>
+        <f t="shared" si="0"/>
+        <v>-0.19358997699727321</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2121,19 +2126,19 @@
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.440078969061093E-2</v>
+        <v>3.040825089971505E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
         <v>149.81253801090318</v>
       </c>
       <c r="I9" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>136.98113905325442</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>141.34261603375526</v>
       </c>
       <c r="J9" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>-8.5649700138682019E-2</v>
+        <f t="shared" si="1"/>
+        <v>-5.6536803191542542E-2</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2145,32 +2150,32 @@
         <v>0.650183652995457</v>
       </c>
       <c r="D10" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.75699017684063397</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.75875011799917746</v>
       </c>
       <c r="E10" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.10680652384517697</v>
+        <f t="shared" si="0"/>
+        <v>0.10856646500372047</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.47368421052631576</v>
+        <v>0.52631578947368418</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.1930826810205707E-3</v>
+        <v>4.8107644875554868E-3</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
         <v>184.92501485879896</v>
       </c>
       <c r="I10" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>192.55856689888213</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>196.07845752743589</v>
       </c>
       <c r="J10" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>4.1279174945108625E-2</v>
+        <f t="shared" si="1"/>
+        <v>6.0313325793988612E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2229,7 +2234,7 @@
         <v>Centro Servizi</v>
       </c>
       <c r="C5" s="41">
-        <f ca="1">IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>10</v>
       </c>
       <c r="D5" s="41">
@@ -2241,11 +2246,11 @@
         <v>0</v>
       </c>
       <c r="F5" s="41">
-        <f ca="1">IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>6</v>
       </c>
       <c r="G5" s="42">
-        <f ca="1">IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
+        <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -2255,8 +2260,8 @@
         <v>Editoria</v>
       </c>
       <c r="C6" s="43">
-        <f ca="1">IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-5</v>
+        <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>2</v>
       </c>
       <c r="D6" s="43">
         <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2267,12 +2272,12 @@
         <v>4</v>
       </c>
       <c r="F6" s="43">
-        <f ca="1">IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>0</v>
       </c>
       <c r="G6" s="42">
-        <f ca="1">IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>1.8</v>
+        <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2281,24 +2286,24 @@
         <v>Gori</v>
       </c>
       <c r="C7" s="41">
-        <f ca="1">IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>-5</v>
+      </c>
+      <c r="D7" s="41">
+        <f>IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
+        <v>10</v>
+      </c>
+      <c r="E7" s="41">
+        <f>IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="41">
+        <f>IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
-      <c r="D7" s="41">
-        <f ca="1">IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>10</v>
-      </c>
-      <c r="E7" s="41">
-        <f ca="1">IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>2</v>
-      </c>
-      <c r="F7" s="41">
-        <f ca="1">IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>4</v>
-      </c>
       <c r="G7" s="42">
-        <f ca="1">IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
-        <v>5.4</v>
+        <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2307,24 +2312,24 @@
         <v>Idrico</v>
       </c>
       <c r="C8" s="43">
-        <f ca="1">IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>2</v>
+        <f>IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>-2</v>
       </c>
       <c r="D8" s="43">
         <f>IF('Dati Comparti'!F7="","",IF('Dati Comparti'!F7&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F7&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F7&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F7&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F7&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="43">
         <f>IF('Dati Comparti'!G7="","",IF('Dati Comparti'!G7&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G7&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G7&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G7&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G7&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="43">
-        <f ca="1">IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>6</v>
       </c>
       <c r="G8" s="42">
-        <f ca="1">IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>1.4</v>
+        <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -2333,7 +2338,7 @@
         <v>Igiene Ambientale</v>
       </c>
       <c r="C9" s="41">
-        <f ca="1">IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D9" s="41">
@@ -2342,15 +2347,15 @@
       </c>
       <c r="E9" s="41">
         <f>IF('Dati Comparti'!G8="","",IF('Dati Comparti'!G8&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G8&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G8&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G8&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G8&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="41">
-        <f ca="1">IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>0</v>
       </c>
       <c r="G9" s="42">
-        <f ca="1">IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>-4</v>
+        <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2358,7 +2363,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="43">
-        <f ca="1">IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D10" s="43">
@@ -2370,11 +2375,11 @@
         <v>2</v>
       </c>
       <c r="F10" s="43">
-        <f ca="1">IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>8</v>
       </c>
       <c r="G10" s="42">
-        <f ca="1">IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
+        <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
         <v>-2.2000000000000002</v>
       </c>
     </row>
@@ -2383,7 +2388,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="41">
-        <f ca="1">IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>10</v>
       </c>
       <c r="D11" s="41">
@@ -2395,12 +2400,12 @@
         <v>0</v>
       </c>
       <c r="F11" s="41">
-        <f ca="1">IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>4</v>
+        <f>IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>2</v>
       </c>
       <c r="G11" s="42">
-        <f ca="1">IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>4.4000000000000004</v>
+        <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
+        <v>4.2</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -2432,15 +2437,15 @@
         <v>13</v>
       </c>
       <c r="C15" s="61" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
-        <v>Gori</v>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
+        <v>Centro Servizi</v>
       </c>
       <c r="D15" s="56"/>
       <c r="E15" s="56"/>
       <c r="F15" s="56"/>
       <c r="G15" s="1">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>5.4</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -2448,14 +2453,14 @@
         <v>14</v>
       </c>
       <c r="C16" s="60" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
         <v>Centro Servizi</v>
       </c>
       <c r="D16" s="56"/>
       <c r="E16" s="56"/>
       <c r="F16" s="56"/>
       <c r="G16" s="2">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -2464,15 +2469,15 @@
         <v>15</v>
       </c>
       <c r="C17" s="58" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
         <v>Medicale</v>
       </c>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
       <c r="F17" s="56"/>
       <c r="G17" s="3">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>4.4000000000000004</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
+        <v>4.2</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -2480,15 +2485,15 @@
         <v>16</v>
       </c>
       <c r="C18" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Editoria</v>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
+        <v>Gori</v>
       </c>
       <c r="D18" s="56"/>
       <c r="E18" s="56"/>
       <c r="F18" s="56"/>
       <c r="G18" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>1.8</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
+        <v>1.4</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -2496,15 +2501,15 @@
         <v>17</v>
       </c>
       <c r="C19" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
         <v>Idrico</v>
       </c>
       <c r="D19" s="56"/>
       <c r="E19" s="56"/>
       <c r="F19" s="56"/>
       <c r="G19" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>1.4</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -2512,14 +2517,14 @@
         <v>18</v>
       </c>
       <c r="C20" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
       <c r="D20" s="56"/>
       <c r="E20" s="56"/>
       <c r="F20" s="56"/>
       <c r="G20" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
         <v>-2.2000000000000002</v>
       </c>
     </row>
@@ -2528,15 +2533,15 @@
         <v>19</v>
       </c>
       <c r="C21" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>Igiene Ambientale</v>
       </c>
       <c r="D21" s="56"/>
       <c r="E21" s="56"/>
       <c r="F21" s="56"/>
       <c r="G21" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
-        <v>-4</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -2570,7 +2575,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3064,26 +3069,187 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="51" t="s">
+      <c r="A22" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="52">
+      <c r="C22" s="54">
         <v>10</v>
       </c>
-      <c r="D22" s="52">
-        <v>0</v>
-      </c>
-      <c r="E22" s="52">
-        <v>0</v>
-      </c>
-      <c r="F22" s="52">
+      <c r="D22" s="54">
+        <v>0</v>
+      </c>
+      <c r="E22" s="54">
+        <v>0</v>
+      </c>
+      <c r="F22" s="54">
         <v>4</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G22" s="54">
         <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="52">
+        <v>10</v>
+      </c>
+      <c r="D23" s="52">
+        <v>0</v>
+      </c>
+      <c r="E23" s="52">
+        <v>0</v>
+      </c>
+      <c r="F23" s="52">
+        <v>6</v>
+      </c>
+      <c r="G23" s="52">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="52">
+        <v>2</v>
+      </c>
+      <c r="D24" s="52">
+        <v>10</v>
+      </c>
+      <c r="E24" s="52">
+        <v>4</v>
+      </c>
+      <c r="F24" s="52">
+        <v>0</v>
+      </c>
+      <c r="G24" s="52">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="52">
+        <v>-5</v>
+      </c>
+      <c r="D25" s="52">
+        <v>10</v>
+      </c>
+      <c r="E25" s="52">
+        <v>0</v>
+      </c>
+      <c r="F25" s="52">
+        <v>4</v>
+      </c>
+      <c r="G25" s="52">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="52">
+        <v>-2</v>
+      </c>
+      <c r="D26" s="52">
+        <v>2</v>
+      </c>
+      <c r="E26" s="52">
+        <v>2</v>
+      </c>
+      <c r="F26" s="52">
+        <v>6</v>
+      </c>
+      <c r="G26" s="52">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D27" s="52">
+        <v>0</v>
+      </c>
+      <c r="E27" s="52">
+        <v>2</v>
+      </c>
+      <c r="F27" s="52">
+        <v>0</v>
+      </c>
+      <c r="G27" s="52">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D28" s="52">
+        <v>2</v>
+      </c>
+      <c r="E28" s="52">
+        <v>2</v>
+      </c>
+      <c r="F28" s="52">
+        <v>8</v>
+      </c>
+      <c r="G28" s="52">
+        <v>-2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="52">
+        <v>10</v>
+      </c>
+      <c r="D29" s="52">
+        <v>0</v>
+      </c>
+      <c r="E29" s="52">
+        <v>0</v>
+      </c>
+      <c r="F29" s="52">
+        <v>2</v>
+      </c>
+      <c r="G29" s="52">
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7BEB3DE-47EA-444F-B85B-EC3DE80E0B09}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12C5A2FB-2142-47F5-9D7D-CFE8F4FA35AF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -994,7 +994,7 @@
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46278</v>
+            <v>46285</v>
           </cell>
         </row>
       </sheetData>
@@ -1056,19 +1056,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.75444606828820626</v>
+            <v>0.74652020900751659</v>
           </cell>
           <cell r="G4">
             <v>0.64516129032258063</v>
           </cell>
           <cell r="H4">
-            <v>-9.5379938521738129E-4</v>
+            <v>-2.429767665068798E-3</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>221.41514400743264</v>
+            <v>223.92589985923991</v>
           </cell>
         </row>
         <row r="5">
@@ -1079,7 +1079,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.76350735068440279</v>
+            <v>0.80037541728285977</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1091,7 +1091,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>282.34175652851758</v>
+            <v>276.97977954867059</v>
           </cell>
         </row>
         <row r="6">
@@ -1102,19 +1102,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.76814494125833666</v>
+            <v>0.74959596855010624</v>
           </cell>
           <cell r="G6">
-            <v>0.96789812296876032</v>
+            <v>0.96097050657868266</v>
           </cell>
           <cell r="H6">
-            <v>7.8981229687603571E-3</v>
+            <v>9.7050657868269496E-4</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>219.03131638456793</v>
+            <v>211.81354938659297</v>
           </cell>
         </row>
         <row r="7">
@@ -1125,19 +1125,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.61652751879606094</v>
+            <v>0.61176125163075323</v>
           </cell>
           <cell r="G7">
-            <v>0.75</v>
+            <v>0.7857142857142857</v>
           </cell>
           <cell r="H7">
-            <v>1.8847809915817124E-2</v>
+            <v>2.6913574139935278E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>193.15833773435438</v>
+            <v>187.77044887523454</v>
           </cell>
         </row>
         <row r="8">
@@ -1148,19 +1148,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.40635494702968061</v>
+            <v>0.41683248812979801</v>
           </cell>
           <cell r="G8">
-            <v>0.5625</v>
+            <v>0.52941176470588236</v>
           </cell>
           <cell r="H8">
-            <v>1.4974432573128546E-2</v>
+            <v>3.9500454623521636E-3</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>253.37864077669903</v>
+            <v>244.39167374681392</v>
           </cell>
         </row>
         <row r="9">
@@ -1171,19 +1171,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.48211556152774671</v>
+            <v>0.52784690498675624</v>
           </cell>
           <cell r="G9">
-            <v>0.75</v>
+            <v>0.625</v>
           </cell>
           <cell r="H9">
-            <v>3.040825089971505E-2</v>
+            <v>2.5690075814470519E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>141.34261603375526</v>
+            <v>141.13362068965517</v>
           </cell>
         </row>
         <row r="10">
@@ -1194,19 +1194,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.75875011799917746</v>
+            <v>0.73007905191624678</v>
           </cell>
           <cell r="G10">
-            <v>0.52631578947368418</v>
+            <v>0.44736842105263158</v>
           </cell>
           <cell r="H10">
-            <v>4.8107644875554868E-3</v>
+            <v>1.115298627665535E-3</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>196.07845752743589</v>
+            <v>195.72241372632558</v>
           </cell>
         </row>
       </sheetData>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D2" s="48">
         <f>'[1]Riepilogo mese per Commessa'!$D$1</f>
-        <v>46278</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1929,11 +1929,11 @@
       </c>
       <c r="D4" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.75444606828820626</v>
+        <v>0.74652020900751659</v>
       </c>
       <c r="E4" s="34">
         <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>0.10451699316306373</v>
+        <v>9.6591133882374058E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>-9.5379938521738129E-4</v>
+        <v>-2.429767665068798E-3</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1949,11 +1949,11 @@
       </c>
       <c r="I4" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>221.41514400743264</v>
+        <v>223.92589985923991</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-4.5921149041381011E-2</v>
+        <v>-3.5102290788173687E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1966,11 +1966,11 @@
       </c>
       <c r="D5" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.76350735068440279</v>
+        <v>0.80037541728285977</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" si="0"/>
-        <v>2.6298628756775688E-3</v>
+        <v>3.9497929474134552E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1986,11 +1986,11 @@
       </c>
       <c r="I5" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>282.34175652851758</v>
+        <v>276.97977954867059</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" si="1"/>
-        <v>0.12545902794649608</v>
+        <v>0.10408533716193602</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -2003,19 +2003,19 @@
       </c>
       <c r="D6" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.76814494125833666</v>
+        <v>0.74959596855010624</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" si="0"/>
-        <v>-2.0642605467414143E-2</v>
+        <v>-3.9191578175644559E-2</v>
       </c>
       <c r="F6" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.96789812296876032</v>
+        <v>0.96097050657868266</v>
       </c>
       <c r="G6" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>7.8981229687603571E-3</v>
+        <v>9.7050657868269496E-4</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -2023,11 +2023,11 @@
       </c>
       <c r="I6" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>219.03131638456793</v>
+        <v>211.81354938659297</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" si="1"/>
-        <v>1.513142598659131E-3</v>
+        <v>-3.1489848151736131E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -2040,19 +2040,19 @@
       </c>
       <c r="D7" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.61652751879606094</v>
+        <v>0.61176125163075323</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
-        <v>-9.4640331520823295E-4</v>
+        <v>-5.7126704805159356E-3</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.75</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.8847809915817124E-2</v>
+        <v>2.6913574139935278E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2060,11 +2060,11 @@
       </c>
       <c r="I7" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>193.15833773435438</v>
+        <v>187.77044887523454</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" si="1"/>
-        <v>-3.7854325591589716E-2</v>
+        <v>-6.4692069283113662E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2077,19 +2077,19 @@
       </c>
       <c r="D8" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.40635494702968061</v>
+        <v>0.41683248812979801</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" si="0"/>
-        <v>-0.22634505297031943</v>
+        <v>-0.21586751187020203</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.5625</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.4974432573128546E-2</v>
+        <v>3.9500454623521636E-3</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2097,11 +2097,11 @@
       </c>
       <c r="I8" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>253.37864077669903</v>
+        <v>244.39167374681392</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="1"/>
-        <v>0.72918826032026907</v>
+        <v>0.66785650071998737</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2114,19 +2114,19 @@
       </c>
       <c r="D9" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.48211556152774671</v>
+        <v>0.52784690498675624</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" si="0"/>
-        <v>-0.19358997699727321</v>
+        <v>-0.14785863353826367</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>3.040825089971505E-2</v>
+        <v>2.5690075814470519E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2134,11 +2134,11 @@
       </c>
       <c r="I9" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>141.34261603375526</v>
+        <v>141.13362068965517</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" si="1"/>
-        <v>-5.6536803191542542E-2</v>
+        <v>-5.7931848939214728E-2</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2151,19 +2151,19 @@
       </c>
       <c r="D10" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.75875011799917746</v>
+        <v>0.73007905191624678</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" si="0"/>
-        <v>0.10856646500372047</v>
+        <v>7.9895398920789784E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.52631578947368418</v>
+        <v>0.44736842105263158</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.8107644875554868E-3</v>
+        <v>1.115298627665535E-3</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2171,11 +2171,11 @@
       </c>
       <c r="I10" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>196.07845752743589</v>
+        <v>195.72241372632558</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="1"/>
-        <v>6.0313325793988612E-2</v>
+        <v>5.8387984317703409E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C6" s="43">
         <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="43">
         <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G6" s="42">
         <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>4.5999999999999996</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2299,11 +2299,11 @@
       </c>
       <c r="F7" s="41">
         <f>IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" s="42">
         <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2325,11 +2325,11 @@
       </c>
       <c r="F8" s="43">
         <f>IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" s="42">
         <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="E9" s="41">
         <f>IF('Dati Comparti'!G8="","",IF('Dati Comparti'!G8&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G8&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G8&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G8&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G8&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="41">
         <f>IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="G9" s="42">
         <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>-3.6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="D10" s="43">
         <f>IF('Dati Comparti'!F9="","",IF('Dati Comparti'!F9&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F9&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F9&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F9&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F9&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="43">
         <f>IF('Dati Comparti'!G9="","",IF('Dati Comparti'!G9&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G9&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G9&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G9&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G9&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G10" s="42">
         <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
-        <v>-2.2000000000000002</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C11" s="41">
         <f>IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" s="41">
         <f>IF('Dati Comparti'!F10="","",IF('Dati Comparti'!F10&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F10&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F10&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F10&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F10&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="G11" s="42">
         <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -2438,14 +2438,14 @@
       </c>
       <c r="C15" s="61" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
+        <v>Editoria</v>
       </c>
       <c r="D15" s="56"/>
       <c r="E15" s="56"/>
       <c r="F15" s="56"/>
       <c r="G15" s="1">
         <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>4.5999999999999996</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -2477,7 +2477,7 @@
       <c r="F17" s="56"/>
       <c r="G17" s="3">
         <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -2493,7 +2493,7 @@
       <c r="F18" s="56"/>
       <c r="G18" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -2509,7 +2509,7 @@
       <c r="F19" s="56"/>
       <c r="G19" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -2525,7 +2525,7 @@
       <c r="F20" s="56"/>
       <c r="G20" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>-2.2000000000000002</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -2541,7 +2541,7 @@
       <c r="F21" s="56"/>
       <c r="G21" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
-        <v>-3.6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -3122,7 +3122,7 @@
         <v>66</v>
       </c>
       <c r="C24" s="52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" s="52">
         <v>10</v>
@@ -3134,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="52">
-        <v>4.5999999999999996</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3154,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G25" s="52">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3177,10 +3177,10 @@
         <v>2</v>
       </c>
       <c r="F26" s="52">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G26" s="52">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3197,13 +3197,13 @@
         <v>0</v>
       </c>
       <c r="E27" s="52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" s="52">
         <v>0</v>
       </c>
       <c r="G27" s="52">
-        <v>-3.6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3217,7 +3217,7 @@
         <v>-10</v>
       </c>
       <c r="D28" s="52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="52">
         <v>2</v>
@@ -3226,7 +3226,7 @@
         <v>8</v>
       </c>
       <c r="G28" s="52">
-        <v>-2.2000000000000002</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3237,7 +3237,7 @@
         <v>8</v>
       </c>
       <c r="C29" s="52">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29" s="52">
         <v>0</v>
@@ -3249,7 +3249,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="52">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12C5A2FB-2142-47F5-9D7D-CFE8F4FA35AF}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6BD2E55-1781-45D1-BC79-0D6755BAC532}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -416,10 +416,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="21">
@@ -994,7 +996,7 @@
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46285</v>
+            <v>46295</v>
           </cell>
         </row>
       </sheetData>
@@ -1056,19 +1058,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.74652020900751659</v>
+            <v>0.70864363279624354</v>
           </cell>
           <cell r="G4">
-            <v>0.64516129032258063</v>
+            <v>0.62903225806451613</v>
           </cell>
           <cell r="H4">
-            <v>-2.429767665068798E-3</v>
+            <v>4.8298065729876702E-3</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>223.92589985923991</v>
+            <v>225.35345464312093</v>
           </cell>
         </row>
         <row r="5">
@@ -1079,7 +1081,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.80037541728285977</v>
+            <v>0.84767133232578862</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1091,7 +1093,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>276.97977954867059</v>
+            <v>274.25778029071546</v>
           </cell>
         </row>
         <row r="6">
@@ -1102,19 +1104,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.74959596855010624</v>
+            <v>0.7578048403079205</v>
           </cell>
           <cell r="G6">
-            <v>0.96097050657868266</v>
+            <v>0.96163607704843579</v>
           </cell>
           <cell r="H6">
-            <v>9.7050657868269496E-4</v>
+            <v>1.6360770484358245E-3</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>211.81354938659297</v>
+            <v>215.08253924156134</v>
           </cell>
         </row>
         <row r="7">
@@ -1125,19 +1127,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.61176125163075323</v>
+            <v>0.59673938762484835</v>
           </cell>
           <cell r="G7">
-            <v>0.7857142857142857</v>
+            <v>0.8571428571428571</v>
           </cell>
           <cell r="H7">
-            <v>2.6913574139935278E-2</v>
+            <v>3.650799441131234E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>187.77044887523454</v>
+            <v>189.58156138226266</v>
           </cell>
         </row>
         <row r="8">
@@ -1148,19 +1150,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.41683248812979801</v>
+            <v>0.42975566579690755</v>
           </cell>
           <cell r="G8">
-            <v>0.52941176470588236</v>
+            <v>0.6470588235294118</v>
           </cell>
           <cell r="H8">
-            <v>3.9500454623521636E-3</v>
+            <v>1.0913002593738397E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>244.39167374681392</v>
+            <v>242.60754115772704</v>
           </cell>
         </row>
         <row r="9">
@@ -1171,19 +1173,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.52784690498675624</v>
+            <v>0.60306823507635887</v>
           </cell>
           <cell r="G9">
-            <v>0.625</v>
+            <v>0.375</v>
           </cell>
           <cell r="H9">
-            <v>2.5690075814470519E-2</v>
+            <v>-2.7944532198813724E-3</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>141.13362068965517</v>
+            <v>146.45995187349604</v>
           </cell>
         </row>
         <row r="10">
@@ -1194,19 +1196,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.73007905191624678</v>
+            <v>0.70170003776092427</v>
           </cell>
           <cell r="G10">
-            <v>0.44736842105263158</v>
+            <v>0.47368421052631576</v>
           </cell>
           <cell r="H10">
-            <v>1.115298627665535E-3</v>
+            <v>-4.5588974227520765E-3</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>195.72241372632558</v>
+            <v>194.04543122466779</v>
           </cell>
         </row>
       </sheetData>
@@ -1887,7 +1889,7 @@
       </c>
       <c r="D2" s="48">
         <f>'[1]Riepilogo mese per Commessa'!$D$1</f>
-        <v>46285</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1929,19 +1931,19 @@
       </c>
       <c r="D4" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.74652020900751659</v>
+        <v>0.70864363279624354</v>
       </c>
       <c r="E4" s="34">
         <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>9.6591133882374058E-2</v>
+        <v>5.8714557671101009E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.64516129032258063</v>
+        <v>0.62903225806451613</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>-2.429767665068798E-3</v>
+        <v>4.8298065729876702E-3</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1949,11 +1951,11 @@
       </c>
       <c r="I4" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>223.92589985923991</v>
+        <v>225.35345464312093</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-3.5102290788173687E-2</v>
+        <v>-2.8950950806478654E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1966,11 +1968,11 @@
       </c>
       <c r="D5" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.80037541728285977</v>
+        <v>0.84767133232578862</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" si="0"/>
-        <v>3.9497929474134552E-2</v>
+        <v>8.6793844517063401E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1986,11 +1988,11 @@
       </c>
       <c r="I5" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>276.97977954867059</v>
+        <v>274.25778029071546</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" si="1"/>
-        <v>0.10408533716193602</v>
+        <v>9.3235016342954211E-2</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -2003,19 +2005,19 @@
       </c>
       <c r="D6" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.74959596855010624</v>
+        <v>0.7578048403079205</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" si="0"/>
-        <v>-3.9191578175644559E-2</v>
+        <v>-3.0982706417830297E-2</v>
       </c>
       <c r="F6" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.96097050657868266</v>
+        <v>0.96163607704843579</v>
       </c>
       <c r="G6" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>9.7050657868269496E-4</v>
+        <v>1.6360770484358245E-3</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -2023,11 +2025,11 @@
       </c>
       <c r="I6" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>211.81354938659297</v>
+        <v>215.08253924156134</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" si="1"/>
-        <v>-3.1489848151736131E-2</v>
+        <v>-1.6542504745260707E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -2040,19 +2042,19 @@
       </c>
       <c r="D7" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.61176125163075323</v>
+        <v>0.59673938762484835</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
-        <v>-5.7126704805159356E-3</v>
+        <v>-2.0734534486420819E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.7857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>2.6913574139935278E-2</v>
+        <v>3.650799441131234E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2060,11 +2062,11 @@
       </c>
       <c r="I7" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>187.77044887523454</v>
+        <v>189.58156138226266</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" si="1"/>
-        <v>-6.4692069283113662E-2</v>
+        <v>-5.5670692908977665E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2077,19 +2079,19 @@
       </c>
       <c r="D8" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.41683248812979801</v>
+        <v>0.42975566579690755</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" si="0"/>
-        <v>-0.21586751187020203</v>
+        <v>-0.20294433420309249</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.52941176470588236</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>3.9500454623521636E-3</v>
+        <v>1.0913002593738397E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2097,11 +2099,11 @@
       </c>
       <c r="I8" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>244.39167374681392</v>
+        <v>242.60754115772704</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="1"/>
-        <v>0.66785650071998737</v>
+        <v>0.65568064754449129</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2114,19 +2116,19 @@
       </c>
       <c r="D9" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.52784690498675624</v>
+        <v>0.60306823507635887</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" si="0"/>
-        <v>-0.14785863353826367</v>
+        <v>-7.2637303448661039E-2</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>2.5690075814470519E-2</v>
+        <v>-2.7944532198813724E-3</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2134,11 +2136,11 @@
       </c>
       <c r="I9" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>141.13362068965517</v>
+        <v>146.45995187349604</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" si="1"/>
-        <v>-5.7931848939214728E-2</v>
+        <v>-2.2378541755718382E-2</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2151,19 +2153,19 @@
       </c>
       <c r="D10" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.73007905191624678</v>
+        <v>0.70170003776092427</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" si="0"/>
-        <v>7.9895398920789784E-2</v>
+        <v>5.1516384765467271E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.44736842105263158</v>
+        <v>0.47368421052631576</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.115298627665535E-3</v>
+        <v>-4.5588974227520765E-3</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2171,11 +2173,11 @@
       </c>
       <c r="I10" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>195.72241372632558</v>
+        <v>194.04543122466779</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="1"/>
-        <v>5.8387984317703409E-2</v>
+        <v>4.931953836982414E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2235,7 +2237,7 @@
       </c>
       <c r="C5" s="41">
         <f>IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D5" s="41">
         <f>IF('Dati Comparti'!F4="","",IF('Dati Comparti'!F4&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F4&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F4&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F4&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F4&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2251,7 +2253,7 @@
       </c>
       <c r="G5" s="42">
         <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
-        <v>4.5999999999999996</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2261,7 +2263,7 @@
       </c>
       <c r="C6" s="43">
         <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D6" s="43">
         <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2273,11 +2275,11 @@
       </c>
       <c r="F6" s="43">
         <f>IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="42">
         <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>5.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2313,15 +2315,15 @@
       </c>
       <c r="C8" s="43">
         <f>IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="D8" s="43">
         <f>IF('Dati Comparti'!F7="","",IF('Dati Comparti'!F7&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F7&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F7&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F7&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F7&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E8" s="43">
         <f>IF('Dati Comparti'!G7="","",IF('Dati Comparti'!G7&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G7&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G7&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G7&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G7&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" s="43">
         <f>IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
@@ -2329,7 +2331,7 @@
       </c>
       <c r="G8" s="42">
         <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -2372,15 +2374,15 @@
       </c>
       <c r="E10" s="43">
         <f>IF('Dati Comparti'!G9="","",IF('Dati Comparti'!G9&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G9&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G9&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G9&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G9&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="43">
         <f>IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" s="42">
         <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
-        <v>-2.8</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
@@ -2389,7 +2391,7 @@
       </c>
       <c r="C11" s="41">
         <f>IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D11" s="41">
         <f>IF('Dati Comparti'!F10="","",IF('Dati Comparti'!F10&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F10&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F10&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F10&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F10&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2405,7 +2407,7 @@
       </c>
       <c r="G11" s="42">
         <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -2445,7 +2447,7 @@
       <c r="F15" s="56"/>
       <c r="G15" s="1">
         <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>5.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -2461,7 +2463,7 @@
       <c r="F16" s="56"/>
       <c r="G16" s="2">
         <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>4.5999999999999996</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2477,7 +2479,7 @@
       <c r="F17" s="56"/>
       <c r="G17" s="3">
         <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -2509,7 +2511,7 @@
       <c r="F19" s="56"/>
       <c r="G19" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -2525,7 +2527,7 @@
       <c r="F20" s="56"/>
       <c r="G20" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>-2.8</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -3099,7 +3101,7 @@
         <v>65</v>
       </c>
       <c r="C23" s="52">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D23" s="52">
         <v>0</v>
@@ -3111,7 +3113,7 @@
         <v>6</v>
       </c>
       <c r="G23" s="52">
-        <v>4.5999999999999996</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3122,7 +3124,7 @@
         <v>66</v>
       </c>
       <c r="C24" s="52">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D24" s="52">
         <v>10</v>
@@ -3131,10 +3133,10 @@
         <v>4</v>
       </c>
       <c r="F24" s="52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="52">
-        <v>5.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3168,19 +3170,19 @@
         <v>68</v>
       </c>
       <c r="C26" s="52">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="D26" s="52">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E26" s="52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" s="52">
         <v>8</v>
       </c>
       <c r="G26" s="52">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3220,13 +3222,13 @@
         <v>0</v>
       </c>
       <c r="E28" s="52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" s="52">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G28" s="52">
-        <v>-2.8</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3237,7 +3239,7 @@
         <v>8</v>
       </c>
       <c r="C29" s="52">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D29" s="52">
         <v>0</v>
@@ -3249,7 +3251,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="52">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6BD2E55-1781-45D1-BC79-0D6755BAC532}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDBC7BA6-06B9-4F50-BD5E-0F66A174D026}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="76">
   <si>
     <t>🏆  SCORING COMPARTI</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
   </si>
 </sst>
 </file>
@@ -975,38 +978,38 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="B1">
-            <v>46266</v>
+            <v>46296</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46295</v>
+            <v>46309</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
       <sheetData sheetId="23">
         <row r="2">
           <cell r="B2" t="str">
@@ -1015,7 +1018,6 @@
           <cell r="D2" t="str">
             <v>PRODUTTIVITÀ</v>
           </cell>
-          <cell r="E2"/>
           <cell r="G2" t="str">
             <v>IUQ</v>
           </cell>
@@ -1025,7 +1027,6 @@
           <cell r="I2" t="str">
             <v>TMG</v>
           </cell>
-          <cell r="J2"/>
         </row>
         <row r="3">
           <cell r="B3" t="str">
@@ -1058,19 +1059,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.70864363279624354</v>
+            <v>0.62389457922256319</v>
           </cell>
           <cell r="G4">
-            <v>0.62903225806451613</v>
+            <v>0.71186440677966101</v>
           </cell>
           <cell r="H4">
-            <v>4.8298065729876702E-3</v>
+            <v>2.363848587107439E-2</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>225.35345464312093</v>
+            <v>239.48593565773959</v>
           </cell>
         </row>
         <row r="5">
@@ -1081,7 +1082,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.84767133232578862</v>
+            <v>0.85336206965098793</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1093,7 +1094,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>274.25778029071546</v>
+            <v>263.94881472652628</v>
           </cell>
         </row>
         <row r="6">
@@ -1104,19 +1105,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.7578048403079205</v>
+            <v>0.8191076312525456</v>
           </cell>
           <cell r="G6">
-            <v>0.96163607704843579</v>
+            <v>0.96459712843375078</v>
           </cell>
           <cell r="H6">
-            <v>1.6360770484358245E-3</v>
+            <v>4.5971284337508189E-3</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>215.08253924156134</v>
+            <v>229.65819343437775</v>
           </cell>
         </row>
         <row r="7">
@@ -1127,19 +1128,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.59673938762484835</v>
+            <v>0.57110872407662172</v>
           </cell>
           <cell r="G7">
-            <v>0.8571428571428571</v>
+            <v>0.85185185185185186</v>
           </cell>
           <cell r="H7">
-            <v>3.650799441131234E-2</v>
+            <v>4.594592248977749E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>189.58156138226266</v>
+            <v>193.4576189403931</v>
           </cell>
         </row>
         <row r="8">
@@ -1150,19 +1151,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.42975566579690755</v>
+            <v>0.34890915043045129</v>
           </cell>
           <cell r="G8">
-            <v>0.6470588235294118</v>
+            <v>0.88235294117647056</v>
           </cell>
           <cell r="H8">
-            <v>1.0913002593738397E-2</v>
+            <v>3.9257936255110218E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>242.60754115772704</v>
+            <v>206.27206771463119</v>
           </cell>
         </row>
         <row r="9">
@@ -1173,19 +1174,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.60306823507635887</v>
+            <v>0.4897538403635317</v>
           </cell>
           <cell r="G9">
-            <v>0.375</v>
+            <v>0.625</v>
           </cell>
           <cell r="H9">
-            <v>-2.7944532198813724E-3</v>
+            <v>1.2578277345227257E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>146.45995187349604</v>
+            <v>170.47017766497461</v>
           </cell>
         </row>
         <row r="10">
@@ -1196,19 +1197,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.70170003776092427</v>
+            <v>0.68084549135326389</v>
           </cell>
           <cell r="G10">
-            <v>0.47368421052631576</v>
+            <v>0.69444444444444442</v>
           </cell>
           <cell r="H10">
-            <v>-4.5588974227520765E-3</v>
+            <v>3.2655195397068307E-2</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>194.04543122466779</v>
+            <v>189.49806697198596</v>
           </cell>
         </row>
       </sheetData>
@@ -1880,7 +1881,7 @@
       </c>
       <c r="D1" s="49">
         <f>'[1]db iniziale'!$B$1</f>
-        <v>46266</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
@@ -1888,8 +1889,8 @@
         <v>56</v>
       </c>
       <c r="D2" s="48">
-        <f>'[1]Riepilogo mese per Commessa'!$D$1</f>
-        <v>46295</v>
+        <f ca="1">'[1]Riepilogo mese per Commessa'!$D$1</f>
+        <v>46309</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1930,32 +1931,32 @@
         <v>0.64992907512514253</v>
       </c>
       <c r="D4" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.70864363279624354</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.62389457922256319</v>
       </c>
       <c r="E4" s="34">
-        <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>5.8714557671101009E-2</v>
+        <f t="shared" ref="E4:E10" ca="1" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
+        <v>-2.6034495902579335E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.62903225806451613</v>
+        <v>0.71186440677966101</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.8298065729876702E-3</v>
+        <v>2.363848587107439E-2</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
         <v>232.07216445995408</v>
       </c>
       <c r="I4" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>225.35345464312093</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>239.48593565773959</v>
       </c>
       <c r="J4" s="34">
-        <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-2.8950950806478654E-2</v>
+        <f t="shared" ref="J4:J10" ca="1" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
+        <v>3.1945973421835402E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1967,12 +1968,12 @@
         <v>0.76087748780872522</v>
       </c>
       <c r="D5" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.84767133232578862</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.85336206965098793</v>
       </c>
       <c r="E5" s="39">
-        <f t="shared" si="0"/>
-        <v>8.6793844517063401E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2484581842262714E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1987,12 +1988,12 @@
         <v>250.86808983502152</v>
       </c>
       <c r="I5" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>274.25778029071546</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>263.94881472652628</v>
       </c>
       <c r="J5" s="39">
-        <f t="shared" si="1"/>
-        <v>9.3235016342954211E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>5.2141844345795593E-2</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -2004,32 +2005,32 @@
         <v>0.7887875467257508</v>
       </c>
       <c r="D6" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.7578048403079205</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.8191076312525456</v>
       </c>
       <c r="E6" s="34">
-        <f t="shared" si="0"/>
-        <v>-3.0982706417830297E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>3.0320084526794799E-2</v>
       </c>
       <c r="F6" s="35">
-        <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.96163607704843579</v>
+        <f ca="1">INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.96459712843375078</v>
       </c>
       <c r="G6" s="36">
-        <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.6360770484358245E-3</v>
+        <f ca="1">INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>4.5971284337508189E-3</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>218.70039150583702</v>
       </c>
       <c r="I6" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>215.08253924156134</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>229.65819343437775</v>
       </c>
       <c r="J6" s="34">
-        <f t="shared" si="1"/>
-        <v>-1.6542504745260707E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>5.0104171524760502E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -2041,32 +2042,32 @@
         <v>0.61747392211126917</v>
       </c>
       <c r="D7" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.59673938762484835</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.57110872407662172</v>
       </c>
       <c r="E7" s="39">
-        <f t="shared" si="0"/>
-        <v>-2.0734534486420819E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-4.6365198034647448E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.8571428571428571</v>
+        <v>0.85185185185185186</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>3.650799441131234E-2</v>
+        <v>4.594592248977749E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
         <v>200.75789235670646</v>
       </c>
       <c r="I7" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>189.58156138226266</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>193.4576189403931</v>
       </c>
       <c r="J7" s="39">
-        <f t="shared" si="1"/>
-        <v>-5.5670692908977665E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-3.6363568727560858E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2078,32 +2079,32 @@
         <v>0.63270000000000004</v>
       </c>
       <c r="D8" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.42975566579690755</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.34890915043045129</v>
       </c>
       <c r="E8" s="34">
-        <f t="shared" si="0"/>
-        <v>-0.20294433420309249</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.28379084956954875</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.6470588235294118</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.0913002593738397E-2</v>
+        <v>3.9257936255110218E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
         <v>146.53039613498757</v>
       </c>
       <c r="I8" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>242.60754115772704</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>206.27206771463119</v>
       </c>
       <c r="J8" s="34">
-        <f t="shared" si="1"/>
-        <v>0.65568064754449129</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0.40770838785290703</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2115,32 +2116,32 @@
         <v>0.67570553852501991</v>
       </c>
       <c r="D9" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.60306823507635887</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.4897538403635317</v>
       </c>
       <c r="E9" s="39">
-        <f t="shared" si="0"/>
-        <v>-7.2637303448661039E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.18595169816148821</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>-2.7944532198813724E-3</v>
+        <v>1.2578277345227257E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
         <v>149.81253801090318</v>
       </c>
       <c r="I9" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>146.45995187349604</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>170.47017766497461</v>
       </c>
       <c r="J9" s="39">
-        <f t="shared" si="1"/>
-        <v>-2.2378541755718382E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0.1378899251581199</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2152,32 +2153,32 @@
         <v>0.650183652995457</v>
       </c>
       <c r="D10" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.70170003776092427</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.68084549135326389</v>
       </c>
       <c r="E10" s="34">
-        <f t="shared" si="0"/>
-        <v>5.1516384765467271E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>3.0661838357806892E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.47368421052631576</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>-4.5588974227520765E-3</v>
+        <v>3.2655195397068307E-2</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
         <v>184.92501485879896</v>
       </c>
       <c r="I10" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>194.04543122466779</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>189.49806697198596</v>
       </c>
       <c r="J10" s="34">
-        <f t="shared" si="1"/>
-        <v>4.931953836982414E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>2.4729223986699668E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2236,24 +2237,24 @@
         <v>Centro Servizi</v>
       </c>
       <c r="C5" s="41">
-        <f>IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>6</v>
+        <f ca="1">IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>-5</v>
       </c>
       <c r="D5" s="41">
         <f>IF('Dati Comparti'!F4="","",IF('Dati Comparti'!F4&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F4&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F4&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F4&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F4&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="41">
         <f>IF('Dati Comparti'!G4="","",IF('Dati Comparti'!G4&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G4&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G4&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G4&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G4&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="41">
-        <f>IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>6</v>
+        <f ca="1">IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>4</v>
       </c>
       <c r="G5" s="42">
-        <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
-        <v>3</v>
+        <f ca="1">IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2262,7 +2263,7 @@
         <v>Editoria</v>
       </c>
       <c r="C6" s="43">
-        <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>10</v>
       </c>
       <c r="D6" s="43">
@@ -2274,11 +2275,11 @@
         <v>4</v>
       </c>
       <c r="F6" s="43">
-        <f>IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>2</v>
       </c>
       <c r="G6" s="42">
-        <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
         <v>8</v>
       </c>
     </row>
@@ -2288,24 +2289,24 @@
         <v>Gori</v>
       </c>
       <c r="C7" s="41">
-        <f>IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-5</v>
+        <f ca="1">IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>4</v>
       </c>
       <c r="D7" s="41">
-        <f>IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
+        <f ca="1">IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
         <v>10</v>
       </c>
       <c r="E7" s="41">
-        <f>IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
+        <f ca="1">IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>0</v>
       </c>
       <c r="F7" s="41">
-        <f>IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>6</v>
+        <f ca="1">IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>2</v>
       </c>
       <c r="G7" s="42">
-        <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
-        <v>1.6</v>
+        <f ca="1">IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
+        <v>4.8</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2314,8 +2315,8 @@
         <v>Idrico</v>
       </c>
       <c r="C8" s="43">
-        <f>IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-5</v>
+        <f ca="1">IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>-10</v>
       </c>
       <c r="D8" s="43">
         <f>IF('Dati Comparti'!F7="","",IF('Dati Comparti'!F7&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F7&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F7&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F7&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F7&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2326,12 +2327,12 @@
         <v>4</v>
       </c>
       <c r="F8" s="43">
-        <f>IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>8</v>
+        <f ca="1">IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>6</v>
       </c>
       <c r="G8" s="42">
-        <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>1.4</v>
+        <f ca="1">IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -2340,24 +2341,24 @@
         <v>Igiene Ambientale</v>
       </c>
       <c r="C9" s="41">
-        <f>IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D9" s="41">
         <f>IF('Dati Comparti'!F8="","",IF('Dati Comparti'!F8&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F8&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F8&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F8&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F8&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E9" s="41">
         <f>IF('Dati Comparti'!G8="","",IF('Dati Comparti'!G8&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G8&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G8&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G8&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G8&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F9" s="41">
-        <f>IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>0</v>
       </c>
       <c r="G9" s="42">
-        <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>-4</v>
+        <f ca="1">IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2365,7 +2366,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="43">
-        <f>IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D10" s="43">
@@ -2374,15 +2375,15 @@
       </c>
       <c r="E10" s="43">
         <f>IF('Dati Comparti'!G9="","",IF('Dati Comparti'!G9&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G9&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G9&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G9&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G9&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="43">
-        <f>IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>6</v>
+        <f ca="1">IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>0</v>
       </c>
       <c r="G10" s="42">
-        <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
-        <v>-3.4</v>
+        <f ca="1">IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
@@ -2390,8 +2391,8 @@
         <v>8</v>
       </c>
       <c r="C11" s="41">
-        <f>IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>6</v>
+        <f ca="1">IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>4</v>
       </c>
       <c r="D11" s="41">
         <f>IF('Dati Comparti'!F10="","",IF('Dati Comparti'!F10&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F10&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F10&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F10&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F10&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2399,15 +2400,15 @@
       </c>
       <c r="E11" s="41">
         <f>IF('Dati Comparti'!G10="","",IF('Dati Comparti'!G10&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G10&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G10&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G10&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G10&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F11" s="41">
-        <f>IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>2</v>
+        <f ca="1">IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>4</v>
       </c>
       <c r="G11" s="42">
-        <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>2.6</v>
+        <f ca="1">IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -2439,14 +2440,14 @@
         <v>13</v>
       </c>
       <c r="C15" s="61" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
         <v>Editoria</v>
       </c>
       <c r="D15" s="56"/>
       <c r="E15" s="56"/>
       <c r="F15" s="56"/>
       <c r="G15" s="1">
-        <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
         <v>8</v>
       </c>
     </row>
@@ -2455,15 +2456,15 @@
         <v>14</v>
       </c>
       <c r="C16" s="60" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
+        <v>Gori</v>
       </c>
       <c r="D16" s="56"/>
       <c r="E16" s="56"/>
       <c r="F16" s="56"/>
       <c r="G16" s="2">
-        <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>3</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
+        <v>4.8</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2471,15 +2472,15 @@
         <v>15</v>
       </c>
       <c r="C17" s="58" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
         <v>Medicale</v>
       </c>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
       <c r="F17" s="56"/>
       <c r="G17" s="3">
-        <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>2.6</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -2487,15 +2488,15 @@
         <v>16</v>
       </c>
       <c r="C18" s="57" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Gori</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
+        <v>Centro Servizi</v>
       </c>
       <c r="D18" s="56"/>
       <c r="E18" s="56"/>
       <c r="F18" s="56"/>
       <c r="G18" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>1.6</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -2503,15 +2504,15 @@
         <v>17</v>
       </c>
       <c r="C19" s="57" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
         <v>Idrico</v>
       </c>
       <c r="D19" s="56"/>
       <c r="E19" s="56"/>
       <c r="F19" s="56"/>
       <c r="G19" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>1.4</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -2519,15 +2520,15 @@
         <v>18</v>
       </c>
       <c r="C20" s="57" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
-        <v>ITS</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
+        <v>Igiene Ambientale</v>
       </c>
       <c r="D20" s="56"/>
       <c r="E20" s="56"/>
       <c r="F20" s="56"/>
       <c r="G20" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>-3.4</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -2535,15 +2536,15 @@
         <v>19</v>
       </c>
       <c r="C21" s="57" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
-        <v>Igiene Ambientale</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
+        <v>ITS</v>
       </c>
       <c r="D21" s="56"/>
       <c r="E21" s="56"/>
       <c r="F21" s="56"/>
       <c r="G21" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
-        <v>-4</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -2577,7 +2578,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3101,7 +3102,7 @@
         <v>65</v>
       </c>
       <c r="C23" s="52">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23" s="52">
         <v>0</v>
@@ -3113,7 +3114,7 @@
         <v>6</v>
       </c>
       <c r="G23" s="52">
-        <v>3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3147,7 +3148,7 @@
         <v>67</v>
       </c>
       <c r="C25" s="52">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D25" s="52">
         <v>10</v>
@@ -3159,7 +3160,7 @@
         <v>6</v>
       </c>
       <c r="G25" s="52">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3232,26 +3233,187 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="52">
+      <c r="C29" s="54">
+        <v>8</v>
+      </c>
+      <c r="D29" s="54">
+        <v>0</v>
+      </c>
+      <c r="E29" s="54">
+        <v>0</v>
+      </c>
+      <c r="F29" s="54">
+        <v>4</v>
+      </c>
+      <c r="G29" s="54">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="52">
+        <v>-5</v>
+      </c>
+      <c r="D30" s="52">
+        <v>2</v>
+      </c>
+      <c r="E30" s="52">
+        <v>2</v>
+      </c>
+      <c r="F30" s="52">
+        <v>4</v>
+      </c>
+      <c r="G30" s="52">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="52">
+        <v>10</v>
+      </c>
+      <c r="D31" s="52">
+        <v>10</v>
+      </c>
+      <c r="E31" s="52">
+        <v>4</v>
+      </c>
+      <c r="F31" s="52">
+        <v>2</v>
+      </c>
+      <c r="G31" s="52">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="52">
+        <v>4</v>
+      </c>
+      <c r="D32" s="52">
+        <v>10</v>
+      </c>
+      <c r="E32" s="52">
+        <v>0</v>
+      </c>
+      <c r="F32" s="52">
+        <v>2</v>
+      </c>
+      <c r="G32" s="52">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D33" s="52">
         <v>6</v>
       </c>
-      <c r="D29" s="52">
-        <v>0</v>
-      </c>
-      <c r="E29" s="52">
-        <v>0</v>
-      </c>
-      <c r="F29" s="52">
+      <c r="E33" s="52">
+        <v>4</v>
+      </c>
+      <c r="F33" s="52">
+        <v>6</v>
+      </c>
+      <c r="G33" s="52">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D34" s="52">
+        <v>6</v>
+      </c>
+      <c r="E34" s="52">
+        <v>4</v>
+      </c>
+      <c r="F34" s="52">
+        <v>0</v>
+      </c>
+      <c r="G34" s="52">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D35" s="52">
+        <v>0</v>
+      </c>
+      <c r="E35" s="52">
         <v>2</v>
       </c>
-      <c r="G29" s="52">
-        <v>2.6</v>
+      <c r="F35" s="52">
+        <v>0</v>
+      </c>
+      <c r="G35" s="52">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="52">
+        <v>4</v>
+      </c>
+      <c r="D36" s="52">
+        <v>0</v>
+      </c>
+      <c r="E36" s="52">
+        <v>4</v>
+      </c>
+      <c r="F36" s="52">
+        <v>4</v>
+      </c>
+      <c r="G36" s="52">
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDBC7BA6-06B9-4F50-BD5E-0F66A174D026}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{588ED78C-DF3A-48B9-9E78-ED583C3933CD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -820,6 +820,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -842,21 +857,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -982,34 +982,34 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46309</v>
+            <v>46313</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
       <sheetData sheetId="23">
         <row r="2">
           <cell r="B2" t="str">
@@ -1018,6 +1018,7 @@
           <cell r="D2" t="str">
             <v>PRODUTTIVITÀ</v>
           </cell>
+          <cell r="E2"/>
           <cell r="G2" t="str">
             <v>IUQ</v>
           </cell>
@@ -1027,6 +1028,7 @@
           <cell r="I2" t="str">
             <v>TMG</v>
           </cell>
+          <cell r="J2"/>
         </row>
         <row r="3">
           <cell r="B3" t="str">
@@ -1059,19 +1061,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.62389457922256319</v>
+            <v>0.62794719262608123</v>
           </cell>
           <cell r="G4">
-            <v>0.71186440677966101</v>
+            <v>0.69354838709677424</v>
           </cell>
           <cell r="H4">
-            <v>2.363848587107439E-2</v>
+            <v>1.2796472454287494E-2</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>239.48593565773959</v>
+            <v>241.48038327074971</v>
           </cell>
         </row>
         <row r="5">
@@ -1082,7 +1084,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.85336206965098793</v>
+            <v>0.8021727782864051</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1094,7 +1096,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>263.94881472652628</v>
+            <v>263.2889829180379</v>
           </cell>
         </row>
         <row r="6">
@@ -1105,19 +1107,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.8191076312525456</v>
+            <v>0.81918279445328013</v>
           </cell>
           <cell r="G6">
-            <v>0.96459712843375078</v>
+            <v>0.96510180713894556</v>
           </cell>
           <cell r="H6">
-            <v>4.5971284337508189E-3</v>
+            <v>5.101807138945591E-3</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>229.65819343437775</v>
+            <v>231.15903229134426</v>
           </cell>
         </row>
         <row r="7">
@@ -1128,19 +1130,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.57110872407662172</v>
+            <v>0.56813147400972419</v>
           </cell>
           <cell r="G7">
-            <v>0.85185185185185186</v>
+            <v>0.88888888888888884</v>
           </cell>
           <cell r="H7">
-            <v>4.594592248977749E-2</v>
+            <v>5.0328852356427554E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>193.4576189403931</v>
+            <v>195.78845822142276</v>
           </cell>
         </row>
         <row r="8">
@@ -1151,19 +1153,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.34890915043045129</v>
+            <v>0.32931588221541236</v>
           </cell>
           <cell r="G8">
-            <v>0.88235294117647056</v>
+            <v>0.94117647058823528</v>
           </cell>
           <cell r="H8">
-            <v>3.9257936255110218E-2</v>
+            <v>4.5486061587353438E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>206.27206771463119</v>
+            <v>203.1070038910506</v>
           </cell>
         </row>
         <row r="9">
@@ -1174,19 +1176,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.4897538403635317</v>
+            <v>0.49440659414707527</v>
           </cell>
           <cell r="G9">
             <v>0.625</v>
           </cell>
           <cell r="H9">
-            <v>1.2578277345227257E-2</v>
+            <v>1.461063050873054E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>170.47017766497461</v>
+            <v>168.34500709891151</v>
           </cell>
         </row>
         <row r="10">
@@ -1197,25 +1199,29 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.68084549135326389</v>
+            <v>0.67408638593533587</v>
           </cell>
           <cell r="G10">
-            <v>0.69444444444444442</v>
+            <v>0.67567567567567566</v>
           </cell>
           <cell r="H10">
-            <v>3.2655195397068307E-2</v>
+            <v>2.9305562636419091E-2</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>189.49806697198596</v>
+            <v>191.7497269251775</v>
           </cell>
         </row>
       </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1419,7 +1425,7 @@
     </row>
     <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="60" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="56"/>
@@ -1494,7 +1500,7 @@
     </row>
     <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="61" t="s">
         <v>36</v>
       </c>
       <c r="C12" s="56"/>
@@ -1599,7 +1605,7 @@
     </row>
     <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="65" t="s">
+      <c r="B23" s="57" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="56"/>
@@ -1682,7 +1688,7 @@
     </row>
     <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="67" t="s">
+      <c r="B32" s="59" t="s">
         <v>47</v>
       </c>
       <c r="C32" s="56"/>
@@ -1765,7 +1771,7 @@
     </row>
     <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="66" t="s">
+      <c r="B41" s="58" t="s">
         <v>52</v>
       </c>
       <c r="C41" s="56"/>
@@ -1889,8 +1895,8 @@
         <v>56</v>
       </c>
       <c r="D2" s="48">
-        <f ca="1">'[1]Riepilogo mese per Commessa'!$D$1</f>
-        <v>46309</v>
+        <f>'[1]Riepilogo mese per Commessa'!$D$1</f>
+        <v>46313</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1931,32 +1937,32 @@
         <v>0.64992907512514253</v>
       </c>
       <c r="D4" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.62389457922256319</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.62794719262608123</v>
       </c>
       <c r="E4" s="34">
-        <f t="shared" ref="E4:E10" ca="1" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>-2.6034495902579335E-2</v>
+        <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
+        <v>-2.19818824990613E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.71186440677966101</v>
+        <v>0.69354838709677424</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>2.363848587107439E-2</v>
+        <v>1.2796472454287494E-2</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
         <v>232.07216445995408</v>
       </c>
       <c r="I4" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>239.48593565773959</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>241.48038327074971</v>
       </c>
       <c r="J4" s="34">
-        <f t="shared" ref="J4:J10" ca="1" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>3.1945973421835402E-2</v>
+        <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
+        <v>4.0540057152865031E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1968,12 +1974,12 @@
         <v>0.76087748780872522</v>
       </c>
       <c r="D5" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.85336206965098793</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.8021727782864051</v>
       </c>
       <c r="E5" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>9.2484581842262714E-2</v>
+        <f t="shared" si="0"/>
+        <v>4.129529047767988E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1988,12 +1994,12 @@
         <v>250.86808983502152</v>
       </c>
       <c r="I5" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>263.94881472652628</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>263.2889829180379</v>
       </c>
       <c r="J5" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>5.2141844345795593E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.9511650091427481E-2</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -2005,32 +2011,32 @@
         <v>0.7887875467257508</v>
       </c>
       <c r="D6" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.8191076312525456</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.81918279445328013</v>
       </c>
       <c r="E6" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.0320084526794799E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.0395247727529329E-2</v>
       </c>
       <c r="F6" s="35">
-        <f ca="1">INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.96459712843375078</v>
+        <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.96510180713894556</v>
       </c>
       <c r="G6" s="36">
-        <f ca="1">INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.5971284337508189E-3</v>
+        <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>5.101807138945591E-3</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>218.70039150583702</v>
       </c>
       <c r="I6" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>229.65819343437775</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>231.15903229134426</v>
       </c>
       <c r="J6" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>5.0104171524760502E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.6966705453633019E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -2042,32 +2048,32 @@
         <v>0.61747392211126917</v>
       </c>
       <c r="D7" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.57110872407662172</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.56813147400972419</v>
       </c>
       <c r="E7" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>-4.6365198034647448E-2</v>
+        <f t="shared" si="0"/>
+        <v>-4.9342448101544978E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.85185185185185186</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.594592248977749E-2</v>
+        <v>5.0328852356427554E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
         <v>200.75789235670646</v>
       </c>
       <c r="I7" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>193.4576189403931</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>195.78845822142276</v>
       </c>
       <c r="J7" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>-3.6363568727560858E-2</v>
+        <f t="shared" si="1"/>
+        <v>-2.4753368731596458E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2079,32 +2085,32 @@
         <v>0.63270000000000004</v>
       </c>
       <c r="D8" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.34890915043045129</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.32931588221541236</v>
       </c>
       <c r="E8" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.28379084956954875</v>
+        <f t="shared" si="0"/>
+        <v>-0.30338411778458768</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.88235294117647056</v>
+        <v>0.94117647058823528</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>3.9257936255110218E-2</v>
+        <v>4.5486061587353438E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
         <v>146.53039613498757</v>
       </c>
       <c r="I8" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>206.27206771463119</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>203.1070038910506</v>
       </c>
       <c r="J8" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.40770838785290703</v>
+        <f t="shared" si="1"/>
+        <v>0.38610833825865865</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2116,12 +2122,12 @@
         <v>0.67570553852501991</v>
       </c>
       <c r="D9" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.4897538403635317</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.49440659414707527</v>
       </c>
       <c r="E9" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.18595169816148821</v>
+        <f t="shared" si="0"/>
+        <v>-0.18129894437794464</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2129,19 +2135,19 @@
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.2578277345227257E-2</v>
+        <v>1.461063050873054E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
         <v>149.81253801090318</v>
       </c>
       <c r="I9" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>170.47017766497461</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>168.34500709891151</v>
       </c>
       <c r="J9" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.1378899251581199</v>
+        <f t="shared" si="1"/>
+        <v>0.1237043930639474</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2153,32 +2159,32 @@
         <v>0.650183652995457</v>
       </c>
       <c r="D10" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.68084549135326389</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.67408638593533587</v>
       </c>
       <c r="E10" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.0661838357806892E-2</v>
+        <f t="shared" si="0"/>
+        <v>2.3902732939878879E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.69444444444444442</v>
+        <v>0.67567567567567566</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>3.2655195397068307E-2</v>
+        <v>2.9305562636419091E-2</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
         <v>184.92501485879896</v>
       </c>
       <c r="I10" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>189.49806697198596</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>191.7497269251775</v>
       </c>
       <c r="J10" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.4729223986699668E-2</v>
+        <f t="shared" si="1"/>
+        <v>3.6905294135515437E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2237,24 +2243,24 @@
         <v>Centro Servizi</v>
       </c>
       <c r="C5" s="41">
-        <f ca="1">IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-5</v>
       </c>
       <c r="D5" s="41">
         <f>IF('Dati Comparti'!F4="","",IF('Dati Comparti'!F4&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F4&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F4&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F4&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F4&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="41">
         <f>IF('Dati Comparti'!G4="","",IF('Dati Comparti'!G4&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G4&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G4&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G4&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G4&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>2</v>
       </c>
       <c r="F5" s="41">
-        <f ca="1">IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G5" s="42">
-        <f ca="1">IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
-        <v>-0.6</v>
+        <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2263,8 +2269,8 @@
         <v>Editoria</v>
       </c>
       <c r="C6" s="43">
-        <f ca="1">IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>10</v>
+        <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>6</v>
       </c>
       <c r="D6" s="43">
         <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2275,12 +2281,12 @@
         <v>4</v>
       </c>
       <c r="F6" s="43">
-        <f ca="1">IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>2</v>
       </c>
       <c r="G6" s="42">
-        <f ca="1">IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>8</v>
+        <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
+        <v>6.4</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2289,23 +2295,23 @@
         <v>Gori</v>
       </c>
       <c r="C7" s="41">
-        <f ca="1">IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>4</v>
       </c>
       <c r="D7" s="41">
-        <f ca="1">IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
+        <f>IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
         <v>10</v>
       </c>
       <c r="E7" s="41">
-        <f ca="1">IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
+        <f>IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>0</v>
       </c>
       <c r="F7" s="41">
-        <f ca="1">IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>2</v>
       </c>
       <c r="G7" s="42">
-        <f ca="1">IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
+        <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
         <v>4.8</v>
       </c>
     </row>
@@ -2315,7 +2321,7 @@
         <v>Idrico</v>
       </c>
       <c r="C8" s="43">
-        <f ca="1">IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D8" s="43">
@@ -2327,11 +2333,11 @@
         <v>4</v>
       </c>
       <c r="F8" s="43">
-        <f ca="1">IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>6</v>
       </c>
       <c r="G8" s="42">
-        <f ca="1">IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
+        <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
         <v>-0.8</v>
       </c>
     </row>
@@ -2341,24 +2347,24 @@
         <v>Igiene Ambientale</v>
       </c>
       <c r="C9" s="41">
-        <f ca="1">IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D9" s="41">
         <f>IF('Dati Comparti'!F8="","",IF('Dati Comparti'!F8&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F8&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F8&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F8&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F8&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" s="41">
         <f>IF('Dati Comparti'!G8="","",IF('Dati Comparti'!G8&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G8&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G8&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G8&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G8&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>4</v>
       </c>
       <c r="F9" s="41">
-        <f ca="1">IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>0</v>
       </c>
       <c r="G9" s="42">
-        <f ca="1">IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>-1.4</v>
+        <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2366,7 +2372,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="43">
-        <f ca="1">IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D10" s="43">
@@ -2378,11 +2384,11 @@
         <v>2</v>
       </c>
       <c r="F10" s="43">
-        <f ca="1">IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>0</v>
       </c>
       <c r="G10" s="42">
-        <f ca="1">IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
+        <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
         <v>-3.6</v>
       </c>
     </row>
@@ -2391,7 +2397,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="41">
-        <f ca="1">IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>4</v>
       </c>
       <c r="D11" s="41">
@@ -2400,19 +2406,19 @@
       </c>
       <c r="E11" s="41">
         <f>IF('Dati Comparti'!G10="","",IF('Dati Comparti'!G10&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G10&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G10&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G10&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G10&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
+        <v>2</v>
+      </c>
+      <c r="F11" s="41">
+        <f>IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
-      <c r="F11" s="41">
-        <f ca="1">IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>4</v>
-      </c>
       <c r="G11" s="42">
-        <f ca="1">IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>2.8</v>
+        <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="67" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="56"/>
@@ -2425,12 +2431,12 @@
       <c r="B14" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="63" t="s">
+      <c r="C14" s="68" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="56"/>
       <c r="E14" s="56"/>
-      <c r="F14" s="64"/>
+      <c r="F14" s="69"/>
       <c r="G14" s="14" t="s">
         <v>12</v>
       </c>
@@ -2439,31 +2445,31 @@
       <c r="B15" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="61" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
+      <c r="C15" s="66" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
         <v>Editoria</v>
       </c>
       <c r="D15" s="56"/>
       <c r="E15" s="56"/>
       <c r="F15" s="56"/>
       <c r="G15" s="1">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>8</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
+        <v>6.4</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="60" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
+      <c r="C16" s="65" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
         <v>Gori</v>
       </c>
       <c r="D16" s="56"/>
       <c r="E16" s="56"/>
       <c r="F16" s="56"/>
       <c r="G16" s="2">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
         <v>4.8</v>
       </c>
     </row>
@@ -2471,47 +2477,47 @@
       <c r="B17" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="58" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
+      <c r="C17" s="63" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
         <v>Medicale</v>
       </c>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
       <c r="F17" s="56"/>
       <c r="G17" s="3">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>2.8</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
+      <c r="C18" s="62" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
+        <v>Idrico</v>
       </c>
       <c r="D18" s="56"/>
       <c r="E18" s="56"/>
       <c r="F18" s="56"/>
       <c r="G18" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>-0.6</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
+      <c r="C19" s="62" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
         <v>Idrico</v>
       </c>
       <c r="D19" s="56"/>
       <c r="E19" s="56"/>
       <c r="F19" s="56"/>
       <c r="G19" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
         <v>-0.8</v>
       </c>
     </row>
@@ -2519,36 +2525,36 @@
       <c r="B20" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
-        <v>Igiene Ambientale</v>
+      <c r="C20" s="62" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
+        <v>Centro Servizi</v>
       </c>
       <c r="D20" s="56"/>
       <c r="E20" s="56"/>
       <c r="F20" s="56"/>
       <c r="G20" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>-1.4</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
+      <c r="C21" s="62" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
       <c r="D21" s="56"/>
       <c r="E21" s="56"/>
       <c r="F21" s="56"/>
       <c r="G21" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
         <v>-3.6</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="59" t="s">
+      <c r="B23" s="64" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="56"/>
@@ -3266,7 +3272,7 @@
         <v>-5</v>
       </c>
       <c r="D30" s="52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" s="52">
         <v>2</v>
@@ -3275,7 +3281,7 @@
         <v>4</v>
       </c>
       <c r="G30" s="52">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3286,7 +3292,7 @@
         <v>66</v>
       </c>
       <c r="C31" s="52">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D31" s="52">
         <v>10</v>
@@ -3298,7 +3304,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="52">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3358,7 +3364,7 @@
         <v>-10</v>
       </c>
       <c r="D34" s="52">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E34" s="52">
         <v>4</v>
@@ -3367,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="52">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3407,13 +3413,13 @@
         <v>0</v>
       </c>
       <c r="E36" s="52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F36" s="52">
         <v>4</v>
       </c>
       <c r="G36" s="52">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{588ED78C-DF3A-48B9-9E78-ED583C3933CD}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF84221C-5AB8-483C-AC04-48B2F8A14265}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -820,21 +820,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -857,6 +842,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -999,7 +999,7 @@
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46313</v>
+            <v>46315</v>
           </cell>
         </row>
       </sheetData>
@@ -1061,19 +1061,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.62794719262608123</v>
+            <v>0.62756200112955662</v>
           </cell>
           <cell r="G4">
-            <v>0.69354838709677424</v>
+            <v>0.67741935483870963</v>
           </cell>
           <cell r="H4">
-            <v>1.2796472454287494E-2</v>
+            <v>1.1330928394135914E-2</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>241.48038327074971</v>
+            <v>240.6381017412086</v>
           </cell>
         </row>
         <row r="5">
@@ -1084,7 +1084,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.8021727782864051</v>
+            <v>0.84123298294248383</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1096,7 +1096,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>263.2889829180379</v>
+            <v>263.6520525129813</v>
           </cell>
         </row>
         <row r="6">
@@ -1107,19 +1107,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.81918279445328013</v>
+            <v>0.82378208286391186</v>
           </cell>
           <cell r="G6">
-            <v>0.96510180713894556</v>
+            <v>0.96539325842696633</v>
           </cell>
           <cell r="H6">
-            <v>5.101807138945591E-3</v>
+            <v>5.393258426966363E-3</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>231.15903229134426</v>
+            <v>230.35986964618249</v>
           </cell>
         </row>
         <row r="7">
@@ -1130,19 +1130,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.56813147400972419</v>
+            <v>0.56802346806473236</v>
           </cell>
           <cell r="G7">
             <v>0.88888888888888884</v>
           </cell>
           <cell r="H7">
-            <v>5.0328852356427554E-2</v>
+            <v>5.2668405110897362E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>195.78845822142276</v>
+            <v>196.2301418279034</v>
           </cell>
         </row>
         <row r="8">
@@ -1153,19 +1153,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.32931588221541236</v>
+            <v>0.33264645169813206</v>
           </cell>
           <cell r="G8">
-            <v>0.94117647058823528</v>
+            <v>1</v>
           </cell>
           <cell r="H8">
-            <v>4.5486061587353438E-2</v>
+            <v>4.6122426339348661E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>203.1070038910506</v>
+            <v>203.31564748201438</v>
           </cell>
         </row>
         <row r="9">
@@ -1176,19 +1176,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.49440659414707527</v>
+            <v>0.5684474985268434</v>
           </cell>
           <cell r="G9">
-            <v>0.625</v>
+            <v>0.75</v>
           </cell>
           <cell r="H9">
-            <v>1.461063050873054E-2</v>
+            <v>4.6185819614170176E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>168.34500709891151</v>
+            <v>168.35711305798915</v>
           </cell>
         </row>
         <row r="10">
@@ -1199,19 +1199,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.67408638593533587</v>
+            <v>0.68115578089439854</v>
           </cell>
           <cell r="G10">
-            <v>0.67567567567567566</v>
+            <v>0.65789473684210531</v>
           </cell>
           <cell r="H10">
-            <v>2.9305562636419091E-2</v>
+            <v>1.5948247197027192E-2</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>191.7497269251775</v>
+            <v>190.70320141371801</v>
           </cell>
         </row>
       </sheetData>
@@ -1425,7 +1425,7 @@
     </row>
     <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="68" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="56"/>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="69" t="s">
         <v>36</v>
       </c>
       <c r="C12" s="56"/>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="65" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="56"/>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="59" t="s">
+      <c r="B32" s="67" t="s">
         <v>47</v>
       </c>
       <c r="C32" s="56"/>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="58" t="s">
+      <c r="B41" s="66" t="s">
         <v>52</v>
       </c>
       <c r="C41" s="56"/>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D2" s="48">
         <f>'[1]Riepilogo mese per Commessa'!$D$1</f>
-        <v>46313</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1938,19 +1938,19 @@
       </c>
       <c r="D4" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.62794719262608123</v>
+        <v>0.62756200112955662</v>
       </c>
       <c r="E4" s="34">
         <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>-2.19818824990613E-2</v>
+        <v>-2.2367073995585907E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.69354838709677424</v>
+        <v>0.67741935483870963</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.2796472454287494E-2</v>
+        <v>1.1330928394135914E-2</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1958,11 +1958,11 @@
       </c>
       <c r="I4" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>241.48038327074971</v>
+        <v>240.6381017412086</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>4.0540057152865031E-2</v>
+        <v>3.691066225537204E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1975,11 +1975,11 @@
       </c>
       <c r="D5" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.8021727782864051</v>
+        <v>0.84123298294248383</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" si="0"/>
-        <v>4.129529047767988E-2</v>
+        <v>8.0355495133758614E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1995,11 +1995,11 @@
       </c>
       <c r="I5" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>263.2889829180379</v>
+        <v>263.6520525129813</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" si="1"/>
-        <v>4.9511650091427481E-2</v>
+        <v>5.0958903088738391E-2</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -2012,19 +2012,19 @@
       </c>
       <c r="D6" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.81918279445328013</v>
+        <v>0.82378208286391186</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" si="0"/>
-        <v>3.0395247727529329E-2</v>
+        <v>3.4994536138161059E-2</v>
       </c>
       <c r="F6" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.96510180713894556</v>
+        <v>0.96539325842696633</v>
       </c>
       <c r="G6" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>5.101807138945591E-3</v>
+        <v>5.393258426966363E-3</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -2032,11 +2032,11 @@
       </c>
       <c r="I6" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>231.15903229134426</v>
+        <v>230.35986964618249</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" si="1"/>
-        <v>5.6966705453633019E-2</v>
+        <v>5.331256181146015E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -2049,11 +2049,11 @@
       </c>
       <c r="D7" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.56813147400972419</v>
+        <v>0.56802346806473236</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
-        <v>-4.9342448101544978E-2</v>
+        <v>-4.9450454046536807E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>5.0328852356427554E-2</v>
+        <v>5.2668405110897362E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2069,11 +2069,11 @@
       </c>
       <c r="I7" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>195.78845822142276</v>
+        <v>196.2301418279034</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" si="1"/>
-        <v>-2.4753368731596458E-2</v>
+        <v>-2.2553287821721921E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2086,19 +2086,19 @@
       </c>
       <c r="D8" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.32931588221541236</v>
+        <v>0.33264645169813206</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" si="0"/>
-        <v>-0.30338411778458768</v>
+        <v>-0.30005354830186798</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.94117647058823528</v>
+        <v>1</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.5486061587353438E-2</v>
+        <v>4.6122426339348661E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2106,11 +2106,11 @@
       </c>
       <c r="I8" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>203.1070038910506</v>
+        <v>203.31564748201438</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="1"/>
-        <v>0.38610833825865865</v>
+        <v>0.38753223116052166</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2123,19 +2123,19 @@
       </c>
       <c r="D9" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.49440659414707527</v>
+        <v>0.5684474985268434</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" si="0"/>
-        <v>-0.18129894437794464</v>
+        <v>-0.10725803999817651</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.461063050873054E-2</v>
+        <v>4.6185819614170176E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2143,11 +2143,11 @@
       </c>
       <c r="I9" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>168.34500709891151</v>
+        <v>168.35711305798915</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" si="1"/>
-        <v>0.1237043930639474</v>
+        <v>0.12378520044654953</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2160,19 +2160,19 @@
       </c>
       <c r="D10" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.67408638593533587</v>
+        <v>0.68115578089439854</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" si="0"/>
-        <v>2.3902732939878879E-2</v>
+        <v>3.0972127898941548E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.67567567567567566</v>
+        <v>0.65789473684210531</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>2.9305562636419091E-2</v>
+        <v>1.5948247197027192E-2</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2180,11 +2180,11 @@
       </c>
       <c r="I10" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>191.7497269251775</v>
+        <v>190.70320141371801</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="1"/>
-        <v>3.6905294135515437E-2</v>
+        <v>3.1246105667916416E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C6" s="43">
         <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D6" s="43">
         <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G6" s="42">
         <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>6.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="E8" s="43">
         <f>IF('Dati Comparti'!G7="","",IF('Dati Comparti'!G7&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G7&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G7&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G7&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G7&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F8" s="43">
         <f>IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="G8" s="42">
         <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="D9" s="41">
         <f>IF('Dati Comparti'!F8="","",IF('Dati Comparti'!F8&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F8&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F8&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F8&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F8&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" s="41">
         <f>IF('Dati Comparti'!G8="","",IF('Dati Comparti'!G8&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G8&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G8&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G8&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G8&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="G9" s="42">
         <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2377,11 +2377,11 @@
       </c>
       <c r="D10" s="43">
         <f>IF('Dati Comparti'!F9="","",IF('Dati Comparti'!F9&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F9&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F9&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F9&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F9&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="43">
         <f>IF('Dati Comparti'!G9="","",IF('Dati Comparti'!G9&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G9&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G9&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G9&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G9&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="43">
         <f>IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G10" s="42">
         <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
-        <v>-3.6</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
@@ -2418,7 +2418,7 @@
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="62" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="56"/>
@@ -2431,12 +2431,12 @@
       <c r="B14" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="63" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="56"/>
       <c r="E14" s="56"/>
-      <c r="F14" s="69"/>
+      <c r="F14" s="64"/>
       <c r="G14" s="14" t="s">
         <v>12</v>
       </c>
@@ -2445,7 +2445,7 @@
       <c r="B15" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="66" t="str">
+      <c r="C15" s="61" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
         <v>Editoria</v>
       </c>
@@ -2454,14 +2454,14 @@
       <c r="F15" s="56"/>
       <c r="G15" s="1">
         <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>6.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="65" t="str">
+      <c r="C16" s="60" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
         <v>Gori</v>
       </c>
@@ -2477,7 +2477,7 @@
       <c r="B17" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="63" t="str">
+      <c r="C17" s="58" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
         <v>Medicale</v>
       </c>
@@ -2493,23 +2493,23 @@
       <c r="B18" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="62" t="str">
+      <c r="C18" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Idrico</v>
+        <v>Igiene Ambientale</v>
       </c>
       <c r="D18" s="56"/>
       <c r="E18" s="56"/>
       <c r="F18" s="56"/>
       <c r="G18" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="62" t="str">
+      <c r="C19" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
         <v>Idrico</v>
       </c>
@@ -2518,14 +2518,14 @@
       <c r="F19" s="56"/>
       <c r="G19" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="62" t="str">
+      <c r="C20" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
         <v>Centro Servizi</v>
       </c>
@@ -2541,7 +2541,7 @@
       <c r="B21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="62" t="str">
+      <c r="C21" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
@@ -2550,11 +2550,11 @@
       <c r="F21" s="56"/>
       <c r="G21" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
-        <v>-3.6</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="59" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="56"/>
@@ -3292,7 +3292,7 @@
         <v>66</v>
       </c>
       <c r="C31" s="52">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D31" s="52">
         <v>10</v>
@@ -3304,7 +3304,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="52">
-        <v>6.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3344,13 +3344,13 @@
         <v>6</v>
       </c>
       <c r="E33" s="52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F33" s="52">
         <v>6</v>
       </c>
       <c r="G33" s="52">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3364,7 +3364,7 @@
         <v>-10</v>
       </c>
       <c r="D34" s="52">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E34" s="52">
         <v>4</v>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="52">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3387,16 +3387,16 @@
         <v>-10</v>
       </c>
       <c r="D35" s="52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35" s="52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35" s="52">
         <v>0</v>
       </c>
       <c r="G35" s="52">
-        <v>-3.6</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF84221C-5AB8-483C-AC04-48B2F8A14265}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1FDBBBD-75EF-45C5-A808-44D6F3D2DE52}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -999,7 +999,7 @@
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46315</v>
+            <v>46320</v>
           </cell>
         </row>
       </sheetData>
@@ -1061,19 +1061,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.62756200112955662</v>
+            <v>0.64124780956004812</v>
           </cell>
           <cell r="G4">
-            <v>0.67741935483870963</v>
+            <v>0.62903225806451613</v>
           </cell>
           <cell r="H4">
-            <v>1.1330928394135914E-2</v>
+            <v>1.1478965319236884E-2</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>240.6381017412086</v>
+            <v>237.72682016179215</v>
           </cell>
         </row>
         <row r="5">
@@ -1084,7 +1084,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.84123298294248383</v>
+            <v>0.82214739334150433</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1096,7 +1096,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>263.6520525129813</v>
+            <v>263.18445371279034</v>
           </cell>
         </row>
         <row r="6">
@@ -1107,19 +1107,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.82378208286391186</v>
+            <v>0.83867702642689546</v>
           </cell>
           <cell r="G6">
-            <v>0.96539325842696633</v>
+            <v>0.9645744826641085</v>
           </cell>
           <cell r="H6">
-            <v>5.393258426966363E-3</v>
+            <v>4.5744826641085368E-3</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>230.35986964618249</v>
+            <v>230.70188960716061</v>
           </cell>
         </row>
         <row r="7">
@@ -1130,19 +1130,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.56802346806473236</v>
+            <v>0.57061615860666171</v>
           </cell>
           <cell r="G7">
-            <v>0.88888888888888884</v>
+            <v>0.8214285714285714</v>
           </cell>
           <cell r="H7">
-            <v>5.2668405110897362E-2</v>
+            <v>4.2108249744231198E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>196.2301418279034</v>
+            <v>198.81609277430866</v>
           </cell>
         </row>
         <row r="8">
@@ -1153,19 +1153,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.33264645169813206</v>
+            <v>0.32373667216768415</v>
           </cell>
           <cell r="G8">
-            <v>1</v>
+            <v>0.94117647058823528</v>
           </cell>
           <cell r="H8">
-            <v>4.6122426339348661E-2</v>
+            <v>4.6225600464108299E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>203.31564748201438</v>
+            <v>202.34825870646767</v>
           </cell>
         </row>
         <row r="9">
@@ -1176,19 +1176,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.5684474985268434</v>
+            <v>0.56816642949045326</v>
           </cell>
           <cell r="G9">
-            <v>0.75</v>
+            <v>0.625</v>
           </cell>
           <cell r="H9">
-            <v>4.6185819614170176E-2</v>
+            <v>4.4497234327733205E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>168.35711305798915</v>
+            <v>169.05715149682493</v>
           </cell>
         </row>
         <row r="10">
@@ -1199,19 +1199,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.68115578089439854</v>
+            <v>0.67145511340079189</v>
           </cell>
           <cell r="G10">
-            <v>0.65789473684210531</v>
+            <v>0.63157894736842102</v>
           </cell>
           <cell r="H10">
-            <v>1.5948247197027192E-2</v>
+            <v>1.8437693329471344E-2</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>190.70320141371801</v>
+            <v>189.24292255110595</v>
           </cell>
         </row>
       </sheetData>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D2" s="48">
         <f>'[1]Riepilogo mese per Commessa'!$D$1</f>
-        <v>46315</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1938,19 +1938,19 @@
       </c>
       <c r="D4" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.62756200112955662</v>
+        <v>0.64124780956004812</v>
       </c>
       <c r="E4" s="34">
         <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>-2.2367073995585907E-2</v>
+        <v>-8.6812655650944093E-3</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.67741935483870963</v>
+        <v>0.62903225806451613</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.1330928394135914E-2</v>
+        <v>1.1478965319236884E-2</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1958,11 +1958,11 @@
       </c>
       <c r="I4" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>240.6381017412086</v>
+        <v>237.72682016179215</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>3.691066225537204E-2</v>
+        <v>2.4365936841226916E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1975,11 +1975,11 @@
       </c>
       <c r="D5" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.84123298294248383</v>
+        <v>0.82214739334150433</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" si="0"/>
-        <v>8.0355495133758614E-2</v>
+        <v>6.1269905532779112E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1995,11 +1995,11 @@
       </c>
       <c r="I5" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>263.6520525129813</v>
+        <v>263.18445371279034</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" si="1"/>
-        <v>5.0958903088738391E-2</v>
+        <v>4.9094980098379343E-2</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -2012,19 +2012,19 @@
       </c>
       <c r="D6" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.82378208286391186</v>
+        <v>0.83867702642689546</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" si="0"/>
-        <v>3.4994536138161059E-2</v>
+        <v>4.9889479701144657E-2</v>
       </c>
       <c r="F6" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.96539325842696633</v>
+        <v>0.9645744826641085</v>
       </c>
       <c r="G6" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>5.393258426966363E-3</v>
+        <v>4.5744826641085368E-3</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -2032,11 +2032,11 @@
       </c>
       <c r="I6" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>230.35986964618249</v>
+        <v>230.70188960716061</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" si="1"/>
-        <v>5.331256181146015E-2</v>
+        <v>5.4876436291168125E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -2049,19 +2049,19 @@
       </c>
       <c r="D7" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.56802346806473236</v>
+        <v>0.57061615860666171</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
-        <v>-4.9450454046536807E-2</v>
+        <v>-4.6857763504607464E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.88888888888888884</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>5.2668405110897362E-2</v>
+        <v>4.2108249744231198E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2069,11 +2069,11 @@
       </c>
       <c r="I7" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>196.2301418279034</v>
+        <v>198.81609277430866</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" si="1"/>
-        <v>-2.2553287821721921E-2</v>
+        <v>-9.6723449305176901E-3</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2086,19 +2086,19 @@
       </c>
       <c r="D8" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.33264645169813206</v>
+        <v>0.32373667216768415</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" si="0"/>
-        <v>-0.30005354830186798</v>
+        <v>-0.30896332783231589</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>1</v>
+        <v>0.94117647058823528</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.6122426339348661E-2</v>
+        <v>4.6225600464108299E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2106,11 +2106,11 @@
       </c>
       <c r="I8" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>203.31564748201438</v>
+        <v>202.34825870646767</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="1"/>
-        <v>0.38753223116052166</v>
+        <v>0.38093026459888402</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2123,19 +2123,19 @@
       </c>
       <c r="D9" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.5684474985268434</v>
+        <v>0.56816642949045326</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" si="0"/>
-        <v>-0.10725803999817651</v>
+        <v>-0.10753910903456665</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.6185819614170176E-2</v>
+        <v>4.4497234327733205E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2143,11 +2143,11 @@
       </c>
       <c r="I9" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>168.35711305798915</v>
+        <v>169.05715149682493</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" si="1"/>
-        <v>0.12378520044654953</v>
+        <v>0.12845796314138372</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2160,19 +2160,19 @@
       </c>
       <c r="D10" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.68115578089439854</v>
+        <v>0.67145511340079189</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" si="0"/>
-        <v>3.0972127898941548E-2</v>
+        <v>2.1271460405334897E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.65789473684210531</v>
+        <v>0.63157894736842102</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.5948247197027192E-2</v>
+        <v>1.8437693329471344E-2</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2180,11 +2180,11 @@
       </c>
       <c r="I10" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>190.70320141371801</v>
+        <v>189.24292255110595</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="1"/>
-        <v>3.1246105667916416E-2</v>
+        <v>2.3349505720488724E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="C5" s="41">
         <f>IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D5" s="41">
         <f>IF('Dati Comparti'!F4="","",IF('Dati Comparti'!F4&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F4&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F4&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F4&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F4&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="G5" s="42">
         <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
-        <v>-1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C6" s="43">
         <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="43">
         <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G6" s="42">
         <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C7" s="41">
         <f>IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" s="41">
         <f>IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G7" s="42">
         <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2326,11 +2326,11 @@
       </c>
       <c r="D8" s="43">
         <f>IF('Dati Comparti'!F7="","",IF('Dati Comparti'!F7&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F7&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F7&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F7&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F7&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" s="43">
         <f>IF('Dati Comparti'!G7="","",IF('Dati Comparti'!G7&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G7&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G7&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G7&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G7&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="43">
         <f>IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="G8" s="42">
         <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>-0.4</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="D9" s="41">
         <f>IF('Dati Comparti'!F8="","",IF('Dati Comparti'!F8&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F8&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F8&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F8&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F8&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9" s="41">
         <f>IF('Dati Comparti'!G8="","",IF('Dati Comparti'!G8&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G8&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G8&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G8&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G8&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="G9" s="42">
         <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D10" s="43">
         <f>IF('Dati Comparti'!F9="","",IF('Dati Comparti'!F9&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F9&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F9&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F9&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F9&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="43">
         <f>IF('Dati Comparti'!G9="","",IF('Dati Comparti'!G9&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G9&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G9&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G9&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G9&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G10" s="42">
         <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
-        <v>-2.6</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
@@ -2454,7 +2454,7 @@
       <c r="F15" s="56"/>
       <c r="G15" s="1">
         <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -2470,7 +2470,7 @@
       <c r="F16" s="56"/>
       <c r="G16" s="2">
         <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2495,14 +2495,14 @@
       </c>
       <c r="C18" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Igiene Ambientale</v>
+        <v>Centro Servizi</v>
       </c>
       <c r="D18" s="56"/>
       <c r="E18" s="56"/>
       <c r="F18" s="56"/>
       <c r="G18" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -2511,14 +2511,14 @@
       </c>
       <c r="C19" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
-        <v>Idrico</v>
+        <v>Igiene Ambientale</v>
       </c>
       <c r="D19" s="56"/>
       <c r="E19" s="56"/>
       <c r="F19" s="56"/>
       <c r="G19" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>-0.4</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="C20" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
+        <v>Idrico</v>
       </c>
       <c r="D20" s="56"/>
       <c r="E20" s="56"/>
       <c r="F20" s="56"/>
       <c r="G20" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -2550,7 +2550,7 @@
       <c r="F21" s="56"/>
       <c r="G21" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
-        <v>-2.6</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -3269,7 +3269,7 @@
         <v>65</v>
       </c>
       <c r="C30" s="52">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D30" s="52">
         <v>0</v>
@@ -3281,7 +3281,7 @@
         <v>4</v>
       </c>
       <c r="G30" s="52">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3292,7 +3292,7 @@
         <v>66</v>
       </c>
       <c r="C31" s="52">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D31" s="52">
         <v>10</v>
@@ -3304,7 +3304,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="52">
-        <v>8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3315,7 +3315,7 @@
         <v>67</v>
       </c>
       <c r="C32" s="52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D32" s="52">
         <v>10</v>
@@ -3327,7 +3327,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="52">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3341,16 +3341,16 @@
         <v>-10</v>
       </c>
       <c r="D33" s="52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E33" s="52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F33" s="52">
         <v>6</v>
       </c>
       <c r="G33" s="52">
-        <v>-0.4</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3364,7 +3364,7 @@
         <v>-10</v>
       </c>
       <c r="D34" s="52">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E34" s="52">
         <v>4</v>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="52">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3387,7 +3387,7 @@
         <v>-10</v>
       </c>
       <c r="D35" s="52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="52">
         <v>4</v>
@@ -3396,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="52">
-        <v>-2.6</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1FDBBBD-75EF-45C5-A808-44D6F3D2DE52}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C378229-FF99-4EB7-A99B-A217C6FB8A95}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -999,7 +999,7 @@
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46320</v>
+            <v>46321</v>
           </cell>
         </row>
       </sheetData>
@@ -1061,19 +1061,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.64124780956004812</v>
+            <v>0.63987653305353032</v>
           </cell>
           <cell r="G4">
-            <v>0.62903225806451613</v>
+            <v>0.61290322580645162</v>
           </cell>
           <cell r="H4">
-            <v>1.1478965319236884E-2</v>
+            <v>1.9894566008145619E-2</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>237.72682016179215</v>
+            <v>238.55829538620156</v>
           </cell>
         </row>
         <row r="5">
@@ -1084,7 +1084,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.82214739334150433</v>
+            <v>0.82250446067332583</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1096,7 +1096,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>263.18445371279034</v>
+            <v>262.9674889259154</v>
           </cell>
         </row>
         <row r="6">
@@ -1107,7 +1107,7 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.83867702642689546</v>
+            <v>0.8323751748345628</v>
           </cell>
           <cell r="G6">
             <v>0.9645744826641085</v>
@@ -1130,19 +1130,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.57061615860666171</v>
+            <v>0.56970181859238656</v>
           </cell>
           <cell r="G7">
-            <v>0.8214285714285714</v>
+            <v>0.8392857142857143</v>
           </cell>
           <cell r="H7">
-            <v>4.2108249744231198E-2</v>
+            <v>4.0759355932015129E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>198.81609277430866</v>
+            <v>198.11584956346542</v>
           </cell>
         </row>
         <row r="8">
@@ -1153,19 +1153,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.32373667216768415</v>
+            <v>0.32377269384964658</v>
           </cell>
           <cell r="G8">
             <v>0.94117647058823528</v>
           </cell>
           <cell r="H8">
-            <v>4.6225600464108299E-2</v>
+            <v>4.3574116087821926E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>202.34825870646767</v>
+            <v>202.23721590909091</v>
           </cell>
         </row>
         <row r="9">
@@ -1176,19 +1176,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.56816642949045326</v>
+            <v>0.56454651791424171</v>
           </cell>
           <cell r="G9">
-            <v>0.625</v>
+            <v>0.75</v>
           </cell>
           <cell r="H9">
-            <v>4.4497234327733205E-2</v>
+            <v>4.5052347661172623E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>169.05715149682493</v>
+            <v>168.92666270783849</v>
           </cell>
         </row>
         <row r="10">
@@ -1199,29 +1199,25 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.67145511340079189</v>
+            <v>0.67060738338935111</v>
           </cell>
           <cell r="G10">
-            <v>0.63157894736842102</v>
+            <v>0.68421052631578949</v>
           </cell>
           <cell r="H10">
-            <v>1.8437693329471344E-2</v>
+            <v>1.9596616974785607E-2</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>189.24292255110595</v>
+            <v>189.306345041257</v>
           </cell>
         </row>
       </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1896,7 +1892,7 @@
       </c>
       <c r="D2" s="48">
         <f>'[1]Riepilogo mese per Commessa'!$D$1</f>
-        <v>46320</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1938,19 +1934,19 @@
       </c>
       <c r="D4" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.64124780956004812</v>
+        <v>0.63987653305353032</v>
       </c>
       <c r="E4" s="34">
         <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>-8.6812655650944093E-3</v>
+        <v>-1.0052542071612214E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.62903225806451613</v>
+        <v>0.61290322580645162</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.1478965319236884E-2</v>
+        <v>1.9894566008145619E-2</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1958,11 +1954,11 @@
       </c>
       <c r="I4" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>237.72682016179215</v>
+        <v>238.55829538620156</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>2.4365936841226916E-2</v>
+        <v>2.7948767321324817E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1975,11 +1971,11 @@
       </c>
       <c r="D5" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.82214739334150433</v>
+        <v>0.82250446067332583</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" si="0"/>
-        <v>6.1269905532779112E-2</v>
+        <v>6.1626972864600615E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1995,11 +1991,11 @@
       </c>
       <c r="I5" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>263.18445371279034</v>
+        <v>262.9674889259154</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" si="1"/>
-        <v>4.9094980098379343E-2</v>
+        <v>4.8230124041885182E-2</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -2012,11 +2008,11 @@
       </c>
       <c r="D6" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.83867702642689546</v>
+        <v>0.8323751748345628</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" si="0"/>
-        <v>4.9889479701144657E-2</v>
+        <v>4.3587628108812004E-2</v>
       </c>
       <c r="F6" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -2049,19 +2045,19 @@
       </c>
       <c r="D7" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.57061615860666171</v>
+        <v>0.56970181859238656</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
-        <v>-4.6857763504607464E-2</v>
+        <v>-4.7772103518882614E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.8214285714285714</v>
+        <v>0.8392857142857143</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.2108249744231198E-2</v>
+        <v>4.0759355932015129E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2069,11 +2065,11 @@
       </c>
       <c r="I7" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>198.81609277430866</v>
+        <v>198.11584956346542</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" si="1"/>
-        <v>-9.6723449305176901E-3</v>
+        <v>-1.3160343348029709E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2086,11 +2082,11 @@
       </c>
       <c r="D8" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.32373667216768415</v>
+        <v>0.32377269384964658</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" si="0"/>
-        <v>-0.30896332783231589</v>
+        <v>-0.30892730615035346</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2098,7 +2094,7 @@
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.6225600464108299E-2</v>
+        <v>4.3574116087821926E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2106,11 +2102,11 @@
       </c>
       <c r="I8" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>202.34825870646767</v>
+        <v>202.23721590909091</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="1"/>
-        <v>0.38093026459888402</v>
+        <v>0.38017245051862675</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2123,19 +2119,19 @@
       </c>
       <c r="D9" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.56816642949045326</v>
+        <v>0.56454651791424171</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" si="0"/>
-        <v>-0.10753910903456665</v>
+        <v>-0.1111590206107782</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.4497234327733205E-2</v>
+        <v>4.5052347661172623E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2143,11 +2139,11 @@
       </c>
       <c r="I9" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>169.05715149682493</v>
+        <v>168.92666270783849</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" si="1"/>
-        <v>0.12845796314138372</v>
+        <v>0.12758694933493619</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2160,19 +2156,19 @@
       </c>
       <c r="D10" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.67145511340079189</v>
+        <v>0.67060738338935111</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" si="0"/>
-        <v>2.1271460405334897E-2</v>
+        <v>2.0423730393894113E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.63157894736842102</v>
+        <v>0.68421052631578949</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.8437693329471344E-2</v>
+        <v>1.9596616974785607E-2</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2180,11 +2176,11 @@
       </c>
       <c r="I10" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>189.24292255110595</v>
+        <v>189.306345041257</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="1"/>
-        <v>2.3349505720488724E-2</v>
+        <v>2.3692469003198106E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2282,11 +2278,11 @@
       </c>
       <c r="F6" s="43">
         <f>IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="42">
         <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2377,7 +2373,7 @@
       </c>
       <c r="D10" s="43">
         <f>IF('Dati Comparti'!F9="","",IF('Dati Comparti'!F9&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F9&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F9&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F9&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F9&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="43">
         <f>IF('Dati Comparti'!G9="","",IF('Dati Comparti'!G9&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G9&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G9&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G9&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G9&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
@@ -2389,7 +2385,7 @@
       </c>
       <c r="G10" s="42">
         <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
-        <v>-3.2</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
@@ -2454,7 +2450,7 @@
       <c r="F15" s="56"/>
       <c r="G15" s="1">
         <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -2550,7 +2546,7 @@
       <c r="F21" s="56"/>
       <c r="G21" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
-        <v>-3.2</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -3301,10 +3297,10 @@
         <v>4</v>
       </c>
       <c r="F31" s="52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="52">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3387,7 +3383,7 @@
         <v>-10</v>
       </c>
       <c r="D35" s="52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35" s="52">
         <v>4</v>
@@ -3396,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="52">
-        <v>-3.2</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
